--- a/artfynd/A 4832-2026 artfynd.xlsx
+++ b/artfynd/A 4832-2026 artfynd.xlsx
@@ -2017,10 +2017,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133570807</v>
+        <v>133570803</v>
       </c>
       <c r="B15" t="n">
-        <v>57955</v>
+        <v>79952</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2028,39 +2028,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>426705</v>
+        <v>426786</v>
       </c>
       <c r="R15" t="n">
-        <v>6799121</v>
+        <v>6798970</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2092,7 +2087,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2102,7 +2097,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2129,7 +2124,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133570803</v>
+        <v>133570804</v>
       </c>
       <c r="B16" t="n">
         <v>79952</v>
@@ -2164,10 +2159,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>426786</v>
+        <v>426780</v>
       </c>
       <c r="R16" t="n">
-        <v>6798970</v>
+        <v>6798974</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2199,7 +2194,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2209,7 +2204,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2236,10 +2231,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133570804</v>
+        <v>133570807</v>
       </c>
       <c r="B17" t="n">
-        <v>79952</v>
+        <v>57955</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2247,34 +2242,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>426780</v>
+        <v>426705</v>
       </c>
       <c r="R17" t="n">
-        <v>6798974</v>
+        <v>6799121</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2450,10 +2450,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133570798</v>
+        <v>133570317</v>
       </c>
       <c r="B19" t="n">
-        <v>79952</v>
+        <v>79091</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2461,21 +2461,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2485,13 +2485,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>426812</v>
+        <v>426745</v>
       </c>
       <c r="R19" t="n">
-        <v>6798874</v>
+        <v>6798943</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2530,7 +2530,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Brandstubbe</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2545,22 +2550,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133570317</v>
+        <v>133570798</v>
       </c>
       <c r="B20" t="n">
-        <v>79091</v>
+        <v>79952</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2568,21 +2573,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2592,13 +2597,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>426745</v>
+        <v>426812</v>
       </c>
       <c r="R20" t="n">
-        <v>6798943</v>
+        <v>6798874</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2627,7 +2632,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2637,12 +2642,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:13</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Brandstubbe</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2657,12 +2657,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3209,10 +3209,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133570801</v>
+        <v>133570789</v>
       </c>
       <c r="B26" t="n">
-        <v>79923</v>
+        <v>79952</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3220,21 +3220,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3244,10 +3244,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>426786</v>
+        <v>426782</v>
       </c>
       <c r="R26" t="n">
-        <v>6798967</v>
+        <v>6798589</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3316,10 +3316,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133570789</v>
+        <v>133570801</v>
       </c>
       <c r="B27" t="n">
-        <v>79952</v>
+        <v>79923</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3327,21 +3327,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3351,10 +3351,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>426782</v>
+        <v>426786</v>
       </c>
       <c r="R27" t="n">
-        <v>6798589</v>
+        <v>6798967</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4075,10 +4075,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133570788</v>
+        <v>133570320</v>
       </c>
       <c r="B34" t="n">
-        <v>79090</v>
+        <v>79091</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4086,37 +4086,40 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>426784</v>
+        <v>426770</v>
       </c>
       <c r="R34" t="n">
-        <v>6798588</v>
+        <v>6798688</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4145,7 +4148,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4155,7 +4158,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4164,25 +4167,26 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133570315</v>
+        <v>133570318</v>
       </c>
       <c r="B35" t="n">
         <v>79952</v>
@@ -4217,10 +4221,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>426759</v>
+        <v>426768</v>
       </c>
       <c r="R35" t="n">
-        <v>6799090</v>
+        <v>6798900</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4252,7 +4256,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4262,12 +4266,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Äldre stubbe</t>
+          <t>Brandstubbe</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4294,7 +4298,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133570318</v>
+        <v>133570791</v>
       </c>
       <c r="B36" t="n">
         <v>79952</v>
@@ -4323,19 +4327,22 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>426768</v>
+        <v>426773</v>
       </c>
       <c r="R36" t="n">
-        <v>6798900</v>
+        <v>6798682</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4364,7 +4371,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4374,12 +4381,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Brandstubbe</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4388,28 +4390,29 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133570791</v>
+        <v>133570788</v>
       </c>
       <c r="B37" t="n">
-        <v>79952</v>
+        <v>79090</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4417,37 +4420,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>426773</v>
+        <v>426784</v>
       </c>
       <c r="R37" t="n">
-        <v>6798682</v>
+        <v>6798588</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4479,7 +4479,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4498,7 +4498,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4517,10 +4516,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133570320</v>
+        <v>133570315</v>
       </c>
       <c r="B38" t="n">
-        <v>79091</v>
+        <v>79952</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4528,37 +4527,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>426770</v>
+        <v>426759</v>
       </c>
       <c r="R38" t="n">
-        <v>6798688</v>
+        <v>6799090</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4590,7 +4586,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4600,7 +4596,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Äldre stubbe</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4609,7 +4610,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -20779,10 +20779,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>133570841</v>
+        <v>133570831</v>
       </c>
       <c r="B195" t="n">
-        <v>79091</v>
+        <v>79952</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20790,21 +20790,21 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -20814,10 +20814,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>426902</v>
+        <v>426892</v>
       </c>
       <c r="R195" t="n">
-        <v>6798724</v>
+        <v>6798794</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20849,7 +20849,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -20859,7 +20859,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -20886,7 +20886,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>133570831</v>
+        <v>133570852</v>
       </c>
       <c r="B196" t="n">
         <v>79952</v>
@@ -20921,10 +20921,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>426892</v>
+        <v>426927</v>
       </c>
       <c r="R196" t="n">
-        <v>6798794</v>
+        <v>6798629</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20956,7 +20956,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -20966,7 +20966,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -20993,48 +20993,53 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>133570342</v>
+        <v>133570752</v>
       </c>
       <c r="B197" t="n">
-        <v>93206</v>
+        <v>57955</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P197" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>427381</v>
+        <v>427462</v>
       </c>
       <c r="R197" t="n">
-        <v>6798673</v>
+        <v>6798577</v>
       </c>
       <c r="S197" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -21063,7 +21068,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -21073,12 +21078,7 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC197" t="inlineStr">
-        <is>
-          <t>4 fruktkroppar</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -21093,44 +21093,44 @@
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>133570852</v>
+        <v>133570342</v>
       </c>
       <c r="B198" t="n">
-        <v>79952</v>
+        <v>93206</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -21140,13 +21140,13 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>426927</v>
+        <v>427381</v>
       </c>
       <c r="R198" t="n">
-        <v>6798629</v>
+        <v>6798673</v>
       </c>
       <c r="S198" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -21175,7 +21175,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -21185,7 +21185,12 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC198" t="inlineStr">
+        <is>
+          <t>4 fruktkroppar</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21200,22 +21205,22 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>133570752</v>
+        <v>133570841</v>
       </c>
       <c r="B199" t="n">
-        <v>57955</v>
+        <v>79091</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -21223,39 +21228,34 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
-      <c r="M199" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P199" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>427462</v>
+        <v>426902</v>
       </c>
       <c r="R199" t="n">
-        <v>6798577</v>
+        <v>6798724</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21287,7 +21287,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -21297,7 +21297,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -21436,48 +21436,52 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>133570363</v>
+        <v>133570747</v>
       </c>
       <c r="B201" t="n">
-        <v>57955</v>
+        <v>93206</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I201" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P201" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>427271</v>
+        <v>427439</v>
       </c>
       <c r="R201" t="n">
-        <v>6798327</v>
+        <v>6798568</v>
       </c>
       <c r="S201" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -21506,7 +21510,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -21516,12 +21520,7 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>16:31</t>
-        </is>
-      </c>
-      <c r="AC201" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -21536,22 +21535,22 @@
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>133570781</v>
+        <v>133570363</v>
       </c>
       <c r="B202" t="n">
-        <v>79090</v>
+        <v>57955</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -21559,21 +21558,21 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -21583,13 +21582,13 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>427226</v>
+        <v>427271</v>
       </c>
       <c r="R202" t="n">
-        <v>6798493</v>
+        <v>6798327</v>
       </c>
       <c r="S202" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -21618,7 +21617,7 @@
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -21628,7 +21627,12 @@
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -21643,65 +21647,60 @@
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>133570787</v>
+        <v>133570311</v>
       </c>
       <c r="B203" t="n">
-        <v>57145</v>
+        <v>57955</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
-      <c r="M203" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P203" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>427144</v>
+        <v>426863</v>
       </c>
       <c r="R203" t="n">
-        <v>6798517</v>
+        <v>6798614</v>
       </c>
       <c r="S203" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T203" t="inlineStr">
         <is>
@@ -21730,7 +21729,7 @@
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
@@ -21740,7 +21739,12 @@
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="AC203" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -21755,60 +21759,65 @@
       <c r="AT203" t="inlineStr"/>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>133570311</v>
+        <v>133570787</v>
       </c>
       <c r="B204" t="n">
-        <v>57955</v>
+        <v>57145</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P204" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>426863</v>
+        <v>427144</v>
       </c>
       <c r="R204" t="n">
-        <v>6798614</v>
+        <v>6798517</v>
       </c>
       <c r="S204" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T204" t="inlineStr">
         <is>
@@ -21837,7 +21846,7 @@
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
@@ -21847,12 +21856,7 @@
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>08:51</t>
-        </is>
-      </c>
-      <c r="AC204" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -21867,61 +21871,57 @@
       <c r="AT204" t="inlineStr"/>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>133570747</v>
+        <v>133570781</v>
       </c>
       <c r="B205" t="n">
-        <v>93206</v>
+        <v>79090</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I205" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>427439</v>
+        <v>427226</v>
       </c>
       <c r="R205" t="n">
-        <v>6798568</v>
+        <v>6798493</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -21953,7 +21953,7 @@
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
@@ -21963,7 +21963,7 @@
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -21990,10 +21990,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>133570764</v>
+        <v>133570846</v>
       </c>
       <c r="B206" t="n">
-        <v>57955</v>
+        <v>79090</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -22001,42 +22001,34 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
-      <c r="K206" t="inlineStr"/>
-      <c r="L206" t="inlineStr"/>
-      <c r="M206" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>427216</v>
+        <v>426923</v>
       </c>
       <c r="R206" t="n">
-        <v>6798740</v>
+        <v>6798703</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -22068,7 +22060,7 @@
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
@@ -22078,7 +22070,7 @@
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -22105,32 +22097,32 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>133570835</v>
+        <v>133570828</v>
       </c>
       <c r="B207" t="n">
-        <v>97995</v>
+        <v>79090</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>221945</v>
+        <v>6446</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -22140,10 +22132,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>426868</v>
+        <v>426913</v>
       </c>
       <c r="R207" t="n">
-        <v>6798759</v>
+        <v>6798802</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -22175,7 +22167,7 @@
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
@@ -22185,12 +22177,7 @@
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>09:42</t>
-        </is>
-      </c>
-      <c r="AC207" t="inlineStr">
-        <is>
-          <t>rikligt med revlummer inom en radie av 4 m</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -22217,10 +22204,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>133570846</v>
+        <v>133570764</v>
       </c>
       <c r="B208" t="n">
-        <v>79090</v>
+        <v>57955</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -22228,34 +22215,42 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
+      <c r="K208" t="inlineStr"/>
+      <c r="L208" t="inlineStr"/>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>426923</v>
+        <v>427216</v>
       </c>
       <c r="R208" t="n">
-        <v>6798703</v>
+        <v>6798740</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -22287,7 +22282,7 @@
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
@@ -22297,7 +22292,7 @@
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -22439,45 +22434,50 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>133570828</v>
+        <v>133570746</v>
       </c>
       <c r="B210" t="n">
-        <v>79090</v>
+        <v>57145</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P210" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>426913</v>
+        <v>427449</v>
       </c>
       <c r="R210" t="n">
-        <v>6798802</v>
+        <v>6798551</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -22509,7 +22509,7 @@
       </c>
       <c r="Z210" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
@@ -22519,7 +22519,7 @@
       </c>
       <c r="AB210" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -22546,32 +22546,32 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>133570829</v>
+        <v>133570334</v>
       </c>
       <c r="B211" t="n">
-        <v>79091</v>
+        <v>57145</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -22581,10 +22581,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>426913</v>
+        <v>427306</v>
       </c>
       <c r="R211" t="n">
-        <v>6798802</v>
+        <v>6798482</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -22616,7 +22616,7 @@
       </c>
       <c r="Z211" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
@@ -22626,7 +22626,12 @@
       </c>
       <c r="AB211" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AC211" t="inlineStr">
+        <is>
+          <t>Färsk spillning, höna</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -22641,22 +22646,22 @@
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>133570746</v>
+        <v>133570835</v>
       </c>
       <c r="B212" t="n">
-        <v>57145</v>
+        <v>97995</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -22664,39 +22669,34 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
-      <c r="M212" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P212" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>427449</v>
+        <v>426868</v>
       </c>
       <c r="R212" t="n">
-        <v>6798551</v>
+        <v>6798759</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -22728,7 +22728,7 @@
       </c>
       <c r="Z212" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
@@ -22738,7 +22738,12 @@
       </c>
       <c r="AB212" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AC212" t="inlineStr">
+        <is>
+          <t>rikligt med revlummer inom en radie av 4 m</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -22765,32 +22770,32 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>133570334</v>
+        <v>133570829</v>
       </c>
       <c r="B213" t="n">
-        <v>57145</v>
+        <v>79091</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -22800,10 +22805,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>427306</v>
+        <v>426913</v>
       </c>
       <c r="R213" t="n">
-        <v>6798482</v>
+        <v>6798802</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -22835,7 +22840,7 @@
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
@@ -22845,12 +22850,7 @@
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>12:57</t>
-        </is>
-      </c>
-      <c r="AC213" t="inlineStr">
-        <is>
-          <t>Färsk spillning, höna</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -22865,12 +22865,12 @@
       <c r="AT213" t="inlineStr"/>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
@@ -22984,53 +22984,45 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>133570783</v>
+        <v>133570729</v>
       </c>
       <c r="B215" t="n">
-        <v>57145</v>
+        <v>79333</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
-      <c r="K215" t="inlineStr"/>
-      <c r="L215" t="inlineStr"/>
-      <c r="M215" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>427211</v>
+        <v>427641</v>
       </c>
       <c r="R215" t="n">
-        <v>6798464</v>
+        <v>6798373</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -23062,7 +23054,7 @@
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
@@ -23072,7 +23064,7 @@
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -23099,10 +23091,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>133570782</v>
+        <v>133570783</v>
       </c>
       <c r="B216" t="n">
-        <v>93206</v>
+        <v>57145</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -23110,38 +23102,42 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I216" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr"/>
+      <c r="K216" t="inlineStr"/>
+      <c r="L216" t="inlineStr"/>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr"/>
       <c r="P216" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>427236</v>
+        <v>427211</v>
       </c>
       <c r="R216" t="n">
-        <v>6798479</v>
+        <v>6798464</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -23173,7 +23169,7 @@
       </c>
       <c r="Z216" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
@@ -23183,7 +23179,7 @@
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -23210,45 +23206,49 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>133570729</v>
+        <v>133570782</v>
       </c>
       <c r="B217" t="n">
-        <v>79333</v>
+        <v>93206</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I217" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P217" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>427641</v>
+        <v>427236</v>
       </c>
       <c r="R217" t="n">
-        <v>6798373</v>
+        <v>6798479</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -23280,7 +23280,7 @@
       </c>
       <c r="Z217" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
@@ -23290,7 +23290,7 @@
       </c>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -23317,32 +23317,32 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>133570838</v>
+        <v>133570361</v>
       </c>
       <c r="B218" t="n">
-        <v>106243</v>
+        <v>79333</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -23352,13 +23352,13 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>426883</v>
+        <v>427570</v>
       </c>
       <c r="R218" t="n">
-        <v>6798787</v>
+        <v>6798357</v>
       </c>
       <c r="S218" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T218" t="inlineStr">
         <is>
@@ -23387,7 +23387,7 @@
       </c>
       <c r="Z218" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
@@ -23397,7 +23397,7 @@
       </c>
       <c r="AB218" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -23412,49 +23412,50 @@
       <c r="AT218" t="inlineStr"/>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>133570753</v>
+        <v>133570786</v>
       </c>
       <c r="B219" t="n">
-        <v>93206</v>
+        <v>57955</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I219" t="inlineStr">
-        <is>
-          <t>4</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr"/>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P219" t="inlineStr">
@@ -23463,10 +23464,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>427505</v>
+        <v>427254</v>
       </c>
       <c r="R219" t="n">
-        <v>6798604</v>
+        <v>6798375</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -23498,7 +23499,7 @@
       </c>
       <c r="Z219" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
@@ -23508,7 +23509,7 @@
       </c>
       <c r="AB219" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -23535,48 +23536,52 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>133570361</v>
+        <v>133570753</v>
       </c>
       <c r="B220" t="n">
-        <v>79333</v>
+        <v>93206</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I220" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P220" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>427570</v>
+        <v>427505</v>
       </c>
       <c r="R220" t="n">
-        <v>6798357</v>
+        <v>6798604</v>
       </c>
       <c r="S220" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T220" t="inlineStr">
         <is>
@@ -23605,7 +23610,7 @@
       </c>
       <c r="Z220" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
@@ -23615,7 +23620,7 @@
       </c>
       <c r="AB220" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -23630,62 +23635,57 @@
       <c r="AT220" t="inlineStr"/>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>133570786</v>
+        <v>133570759</v>
       </c>
       <c r="B221" t="n">
-        <v>57955</v>
+        <v>93206</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
-      <c r="M221" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P221" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>427254</v>
+        <v>427425</v>
       </c>
       <c r="R221" t="n">
-        <v>6798375</v>
+        <v>6798648</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -23717,7 +23717,7 @@
       </c>
       <c r="Z221" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
@@ -23727,7 +23727,7 @@
       </c>
       <c r="AB221" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -23754,10 +23754,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>133570759</v>
+        <v>133570838</v>
       </c>
       <c r="B222" t="n">
-        <v>93206</v>
+        <v>106243</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -23765,21 +23765,21 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>4364</v>
+        <v>221725</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -23789,10 +23789,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>427425</v>
+        <v>426883</v>
       </c>
       <c r="R222" t="n">
-        <v>6798648</v>
+        <v>6798787</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -23824,7 +23824,7 @@
       </c>
       <c r="Z222" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -23861,57 +23861,48 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>133570858</v>
+        <v>133570357</v>
       </c>
       <c r="B223" t="n">
-        <v>8455</v>
+        <v>79333</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
-      <c r="J223" t="inlineStr"/>
-      <c r="K223" t="inlineStr"/>
-      <c r="L223" t="inlineStr"/>
-      <c r="M223" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>426896</v>
+        <v>427541</v>
       </c>
       <c r="R223" t="n">
-        <v>6798616</v>
+        <v>6798424</v>
       </c>
       <c r="S223" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T223" t="inlineStr">
         <is>
@@ -23940,7 +23931,7 @@
       </c>
       <c r="Z223" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
@@ -23950,7 +23941,7 @@
       </c>
       <c r="AB223" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -23959,26 +23950,25 @@
       <c r="AE223" t="b">
         <v>0</v>
       </c>
-      <c r="AF223" t="inlineStr"/>
       <c r="AG223" t="b">
         <v>0</v>
       </c>
       <c r="AT223" t="inlineStr"/>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>133570357</v>
+        <v>133570740</v>
       </c>
       <c r="B224" t="n">
         <v>79333</v>
@@ -24013,13 +24003,13 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>427541</v>
+        <v>427511</v>
       </c>
       <c r="R224" t="n">
-        <v>6798424</v>
+        <v>6798460</v>
       </c>
       <c r="S224" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T224" t="inlineStr">
         <is>
@@ -24048,7 +24038,7 @@
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
@@ -24058,7 +24048,7 @@
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -24073,22 +24063,22 @@
       <c r="AT224" t="inlineStr"/>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>133570740</v>
+        <v>133570819</v>
       </c>
       <c r="B225" t="n">
-        <v>79333</v>
+        <v>79952</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -24096,21 +24086,21 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -24120,10 +24110,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>427511</v>
+        <v>426851</v>
       </c>
       <c r="R225" t="n">
-        <v>6798460</v>
+        <v>6798891</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -24155,7 +24145,7 @@
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
@@ -24165,7 +24155,7 @@
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -24192,32 +24182,32 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>133570333</v>
+        <v>133570767</v>
       </c>
       <c r="B226" t="n">
-        <v>57145</v>
+        <v>79090</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -24227,13 +24217,13 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>427308</v>
+        <v>427270</v>
       </c>
       <c r="R226" t="n">
-        <v>6798484</v>
+        <v>6798722</v>
       </c>
       <c r="S226" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="T226" t="inlineStr">
         <is>
@@ -24262,7 +24252,7 @@
       </c>
       <c r="Z226" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
@@ -24272,12 +24262,7 @@
       </c>
       <c r="AB226" t="inlineStr">
         <is>
-          <t>12:56</t>
-        </is>
-      </c>
-      <c r="AC226" t="inlineStr">
-        <is>
-          <t>Färsk spillning, tupp</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -24292,22 +24277,22 @@
       <c r="AT226" t="inlineStr"/>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>133570720</v>
+        <v>133570328</v>
       </c>
       <c r="B227" t="n">
-        <v>57955</v>
+        <v>79090</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -24315,42 +24300,37 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
-      <c r="M227" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P227" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>427401</v>
+        <v>427277</v>
       </c>
       <c r="R227" t="n">
-        <v>6798415</v>
+        <v>6798465</v>
       </c>
       <c r="S227" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T227" t="inlineStr">
         <is>
@@ -24379,7 +24359,7 @@
       </c>
       <c r="Z227" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
@@ -24389,7 +24369,12 @@
       </c>
       <c r="AB227" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AC227" t="inlineStr">
+        <is>
+          <t>Brandstubbe</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -24404,22 +24389,22 @@
       <c r="AT227" t="inlineStr"/>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>133570819</v>
+        <v>133570720</v>
       </c>
       <c r="B228" t="n">
-        <v>79952</v>
+        <v>57955</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -24427,34 +24412,39 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P228" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>426851</v>
+        <v>427401</v>
       </c>
       <c r="R228" t="n">
-        <v>6798891</v>
+        <v>6798415</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -24486,7 +24476,7 @@
       </c>
       <c r="Z228" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
@@ -24496,7 +24486,7 @@
       </c>
       <c r="AB228" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -24523,45 +24513,53 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>133570767</v>
+        <v>133570756</v>
       </c>
       <c r="B229" t="n">
-        <v>79090</v>
+        <v>57950</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6446</v>
+        <v>100110</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
+      <c r="K229" t="inlineStr"/>
+      <c r="L229" t="inlineStr"/>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr"/>
       <c r="P229" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>427270</v>
+        <v>427481</v>
       </c>
       <c r="R229" t="n">
-        <v>6798722</v>
+        <v>6798627</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -24593,7 +24591,7 @@
       </c>
       <c r="Z229" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
@@ -24603,7 +24601,12 @@
       </c>
       <c r="AB229" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AC229" t="inlineStr">
+        <is>
+          <t>Sågs flyga från trädstam till trädstam och gav även ifrån sig ett läte.</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -24623,39 +24626,39 @@
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Eva Löfqvist, Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>133570824</v>
+        <v>133570333</v>
       </c>
       <c r="B230" t="n">
-        <v>79091</v>
+        <v>57145</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -24665,13 +24668,13 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>426915</v>
+        <v>427308</v>
       </c>
       <c r="R230" t="n">
-        <v>6798823</v>
+        <v>6798484</v>
       </c>
       <c r="S230" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="T230" t="inlineStr">
         <is>
@@ -24700,7 +24703,7 @@
       </c>
       <c r="Z230" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
@@ -24710,7 +24713,12 @@
       </c>
       <c r="AB230" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AC230" t="inlineStr">
+        <is>
+          <t>Färsk spillning, tupp</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -24725,22 +24733,22 @@
       <c r="AT230" t="inlineStr"/>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>133570756</v>
+        <v>133570858</v>
       </c>
       <c r="B231" t="n">
-        <v>57950</v>
+        <v>8455</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -24748,29 +24756,30 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>100110</v>
+        <v>106545</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
+      <c r="J231" t="inlineStr"/>
       <c r="K231" t="inlineStr"/>
       <c r="L231" t="inlineStr"/>
       <c r="M231" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N231" t="inlineStr"/>
@@ -24780,10 +24789,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>427481</v>
+        <v>426896</v>
       </c>
       <c r="R231" t="n">
-        <v>6798627</v>
+        <v>6798616</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -24815,7 +24824,7 @@
       </c>
       <c r="Z231" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
@@ -24825,12 +24834,7 @@
       </c>
       <c r="AB231" t="inlineStr">
         <is>
-          <t>14:06</t>
-        </is>
-      </c>
-      <c r="AC231" t="inlineStr">
-        <is>
-          <t>Sågs flyga från trädstam till trädstam och gav även ifrån sig ett läte.</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -24839,6 +24843,7 @@
       <c r="AE231" t="b">
         <v>0</v>
       </c>
+      <c r="AF231" t="inlineStr"/>
       <c r="AG231" t="b">
         <v>0</v>
       </c>
@@ -24850,17 +24855,17 @@
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>133570328</v>
+        <v>133570824</v>
       </c>
       <c r="B232" t="n">
-        <v>79090</v>
+        <v>79091</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -24868,21 +24873,21 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -24892,13 +24897,13 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>427277</v>
+        <v>426915</v>
       </c>
       <c r="R232" t="n">
-        <v>6798465</v>
+        <v>6798823</v>
       </c>
       <c r="S232" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T232" t="inlineStr">
         <is>
@@ -24927,7 +24932,7 @@
       </c>
       <c r="Z232" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
@@ -24937,12 +24942,7 @@
       </c>
       <c r="AB232" t="inlineStr">
         <is>
-          <t>12:46</t>
-        </is>
-      </c>
-      <c r="AC232" t="inlineStr">
-        <is>
-          <t>Brandstubbe</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -24957,57 +24957,60 @@
       <c r="AT232" t="inlineStr"/>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>133570840</v>
+        <v>133570821</v>
       </c>
       <c r="B233" t="n">
-        <v>106243</v>
+        <v>79952</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>221725</v>
+        <v>6453</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
+      <c r="J233" t="inlineStr"/>
+      <c r="K233" t="inlineStr"/>
+      <c r="N233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>426891</v>
+        <v>426889</v>
       </c>
       <c r="R233" t="n">
-        <v>6798759</v>
+        <v>6798863</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -25039,7 +25042,7 @@
       </c>
       <c r="Z233" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
@@ -25049,7 +25052,7 @@
       </c>
       <c r="AB233" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -25058,6 +25061,7 @@
       <c r="AE233" t="b">
         <v>0</v>
       </c>
+      <c r="AF233" t="inlineStr"/>
       <c r="AG233" t="b">
         <v>0</v>
       </c>
@@ -25076,7 +25080,7 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>133570821</v>
+        <v>133570863</v>
       </c>
       <c r="B234" t="n">
         <v>79952</v>
@@ -25105,19 +25109,16 @@
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
-      <c r="J234" t="inlineStr"/>
-      <c r="K234" t="inlineStr"/>
-      <c r="N234" t="inlineStr"/>
       <c r="P234" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>426889</v>
+        <v>426879</v>
       </c>
       <c r="R234" t="n">
-        <v>6798863</v>
+        <v>6798612</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -25149,7 +25150,7 @@
       </c>
       <c r="Z234" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
@@ -25159,7 +25160,7 @@
       </c>
       <c r="AB234" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD234" t="b">
@@ -25168,7 +25169,6 @@
       <c r="AE234" t="b">
         <v>0</v>
       </c>
-      <c r="AF234" t="inlineStr"/>
       <c r="AG234" t="b">
         <v>0</v>
       </c>
@@ -25187,32 +25187,32 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>133570863</v>
+        <v>133570840</v>
       </c>
       <c r="B235" t="n">
-        <v>79952</v>
+        <v>106243</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>6453</v>
+        <v>221725</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
@@ -25222,10 +25222,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>426879</v>
+        <v>426891</v>
       </c>
       <c r="R235" t="n">
-        <v>6798612</v>
+        <v>6798759</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -25257,7 +25257,7 @@
       </c>
       <c r="Z235" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA235" t="inlineStr">
@@ -25267,7 +25267,7 @@
       </c>
       <c r="AB235" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -25406,42 +25406,37 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>133570834</v>
+        <v>133570847</v>
       </c>
       <c r="B237" t="n">
-        <v>58332</v>
+        <v>79091</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>103015</v>
+        <v>228912</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
+      <c r="J237" t="inlineStr"/>
       <c r="K237" t="inlineStr"/>
-      <c r="L237" t="inlineStr"/>
-      <c r="M237" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
@@ -25449,10 +25444,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>426859</v>
+        <v>426923</v>
       </c>
       <c r="R237" t="n">
-        <v>6798762</v>
+        <v>6798702</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -25484,7 +25479,7 @@
       </c>
       <c r="Z237" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
@@ -25494,7 +25489,7 @@
       </c>
       <c r="AB237" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -25503,6 +25498,7 @@
       <c r="AE237" t="b">
         <v>0</v>
       </c>
+      <c r="AF237" t="inlineStr"/>
       <c r="AG237" t="b">
         <v>0</v>
       </c>
@@ -25632,10 +25628,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>133570847</v>
+        <v>133570349</v>
       </c>
       <c r="B239" t="n">
-        <v>79091</v>
+        <v>79090</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -25643,21 +25639,21 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -25670,13 +25666,13 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>426923</v>
+        <v>427511</v>
       </c>
       <c r="R239" t="n">
-        <v>6798702</v>
+        <v>6798572</v>
       </c>
       <c r="S239" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T239" t="inlineStr">
         <is>
@@ -25705,7 +25701,7 @@
       </c>
       <c r="Z239" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
@@ -25715,7 +25711,7 @@
       </c>
       <c r="AB239" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -25731,22 +25727,22 @@
       <c r="AT239" t="inlineStr"/>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>133570349</v>
+        <v>133570785</v>
       </c>
       <c r="B240" t="n">
-        <v>79090</v>
+        <v>57955</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -25754,40 +25750,42 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
-      <c r="J240" t="inlineStr"/>
-      <c r="K240" t="inlineStr"/>
-      <c r="N240" t="inlineStr"/>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P240" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>427511</v>
+        <v>427253</v>
       </c>
       <c r="R240" t="n">
-        <v>6798572</v>
+        <v>6798390</v>
       </c>
       <c r="S240" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T240" t="inlineStr">
         <is>
@@ -25816,7 +25814,7 @@
       </c>
       <c r="Z240" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA240" t="inlineStr">
@@ -25826,7 +25824,7 @@
       </c>
       <c r="AB240" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD240" t="b">
@@ -25835,46 +25833,45 @@
       <c r="AE240" t="b">
         <v>0</v>
       </c>
-      <c r="AF240" t="inlineStr"/>
       <c r="AG240" t="b">
         <v>0</v>
       </c>
       <c r="AT240" t="inlineStr"/>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>133570785</v>
+        <v>133570834</v>
       </c>
       <c r="B241" t="n">
-        <v>57955</v>
+        <v>58332</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -25883,21 +25880,24 @@
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
+      <c r="K241" t="inlineStr"/>
+      <c r="L241" t="inlineStr"/>
       <c r="M241" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N241" t="inlineStr"/>
       <c r="P241" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>427253</v>
+        <v>426859</v>
       </c>
       <c r="R241" t="n">
-        <v>6798390</v>
+        <v>6798762</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -25929,7 +25929,7 @@
       </c>
       <c r="Z241" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA241" t="inlineStr">
@@ -25939,7 +25939,7 @@
       </c>
       <c r="AB241" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD241" t="b">
@@ -25966,45 +25966,50 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>133570815</v>
+        <v>133570776</v>
       </c>
       <c r="B242" t="n">
-        <v>79090</v>
+        <v>57145</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P242" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>426859</v>
+        <v>427301</v>
       </c>
       <c r="R242" t="n">
-        <v>6798952</v>
+        <v>6798484</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -26036,7 +26041,7 @@
       </c>
       <c r="Z242" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
@@ -26046,7 +26051,7 @@
       </c>
       <c r="AB242" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -26073,10 +26078,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>133570832</v>
+        <v>133570851</v>
       </c>
       <c r="B243" t="n">
-        <v>58119</v>
+        <v>79952</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -26084,42 +26089,34 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
-      <c r="K243" t="inlineStr"/>
-      <c r="L243" t="inlineStr"/>
-      <c r="M243" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N243" t="inlineStr"/>
       <c r="P243" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>426882</v>
+        <v>426929</v>
       </c>
       <c r="R243" t="n">
-        <v>6798778</v>
+        <v>6798628</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -26151,7 +26148,7 @@
       </c>
       <c r="Z243" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr">
@@ -26161,7 +26158,7 @@
       </c>
       <c r="AB243" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -26188,50 +26185,45 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>133570776</v>
+        <v>133570815</v>
       </c>
       <c r="B244" t="n">
-        <v>57145</v>
+        <v>79090</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
-      <c r="M244" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P244" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>427301</v>
+        <v>426859</v>
       </c>
       <c r="R244" t="n">
-        <v>6798484</v>
+        <v>6798952</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -26263,7 +26255,7 @@
       </c>
       <c r="Z244" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
@@ -26273,7 +26265,7 @@
       </c>
       <c r="AB244" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -26407,10 +26399,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>133570851</v>
+        <v>133570832</v>
       </c>
       <c r="B246" t="n">
-        <v>79952</v>
+        <v>58119</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -26418,34 +26410,42 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
+      <c r="K246" t="inlineStr"/>
+      <c r="L246" t="inlineStr"/>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N246" t="inlineStr"/>
       <c r="P246" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>426929</v>
+        <v>426882</v>
       </c>
       <c r="R246" t="n">
-        <v>6798628</v>
+        <v>6798778</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -26477,7 +26477,7 @@
       </c>
       <c r="Z246" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
@@ -26487,7 +26487,7 @@
       </c>
       <c r="AB246" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -26514,10 +26514,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>133570861</v>
+        <v>133570816</v>
       </c>
       <c r="B247" t="n">
-        <v>79091</v>
+        <v>79952</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -26525,21 +26525,21 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
@@ -26549,10 +26549,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>426896</v>
+        <v>426859</v>
       </c>
       <c r="R247" t="n">
-        <v>6798604</v>
+        <v>6798955</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -26584,7 +26584,7 @@
       </c>
       <c r="Z247" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA247" t="inlineStr">
@@ -26594,7 +26594,7 @@
       </c>
       <c r="AB247" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD247" t="b">
@@ -26621,10 +26621,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>133570732</v>
+        <v>133570827</v>
       </c>
       <c r="B248" t="n">
-        <v>57958</v>
+        <v>79952</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -26632,42 +26632,34 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
-      <c r="K248" t="inlineStr"/>
-      <c r="L248" t="inlineStr"/>
-      <c r="M248" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N248" t="inlineStr"/>
       <c r="P248" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>427617</v>
+        <v>426914</v>
       </c>
       <c r="R248" t="n">
-        <v>6798425</v>
+        <v>6798802</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -26699,7 +26691,7 @@
       </c>
       <c r="Z248" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
@@ -26709,12 +26701,7 @@
       </c>
       <c r="AB248" t="inlineStr">
         <is>
-          <t>15:10</t>
-        </is>
-      </c>
-      <c r="AC248" t="inlineStr">
-        <is>
-          <t>färska ringhack med kåda.</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -26741,48 +26728,56 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>133570358</v>
+        <v>133570732</v>
       </c>
       <c r="B249" t="n">
-        <v>57145</v>
+        <v>57958</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
+      <c r="K249" t="inlineStr"/>
+      <c r="L249" t="inlineStr"/>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>427596</v>
+        <v>427617</v>
       </c>
       <c r="R249" t="n">
-        <v>6798420</v>
+        <v>6798425</v>
       </c>
       <c r="S249" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T249" t="inlineStr">
         <is>
@@ -26811,7 +26806,7 @@
       </c>
       <c r="Z249" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA249" t="inlineStr">
@@ -26821,12 +26816,12 @@
       </c>
       <c r="AB249" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC249" t="inlineStr">
         <is>
-          <t>Färsk spillning tupp</t>
+          <t>färska ringhack med kåda.</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -26841,44 +26836,44 @@
       <c r="AT249" t="inlineStr"/>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>133570816</v>
+        <v>133570358</v>
       </c>
       <c r="B250" t="n">
-        <v>79952</v>
+        <v>57145</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
@@ -26888,13 +26883,13 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>426859</v>
+        <v>427596</v>
       </c>
       <c r="R250" t="n">
-        <v>6798955</v>
+        <v>6798420</v>
       </c>
       <c r="S250" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T250" t="inlineStr">
         <is>
@@ -26923,7 +26918,7 @@
       </c>
       <c r="Z250" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
@@ -26933,7 +26928,12 @@
       </c>
       <c r="AB250" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AC250" t="inlineStr">
+        <is>
+          <t>Färsk spillning tupp</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -26948,22 +26948,22 @@
       <c r="AT250" t="inlineStr"/>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>133570827</v>
+        <v>133570861</v>
       </c>
       <c r="B251" t="n">
-        <v>79952</v>
+        <v>79091</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -26971,21 +26971,21 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
@@ -26995,10 +26995,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>426914</v>
+        <v>426896</v>
       </c>
       <c r="R251" t="n">
-        <v>6798802</v>
+        <v>6798604</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -27030,7 +27030,7 @@
       </c>
       <c r="Z251" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA251" t="inlineStr">
@@ -27040,7 +27040,7 @@
       </c>
       <c r="AB251" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -27067,32 +27067,32 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>133570335</v>
+        <v>133570860</v>
       </c>
       <c r="B252" t="n">
-        <v>57145</v>
+        <v>79952</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -27102,13 +27102,13 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>427278</v>
+        <v>426896</v>
       </c>
       <c r="R252" t="n">
-        <v>6798720</v>
+        <v>6798604</v>
       </c>
       <c r="S252" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="T252" t="inlineStr">
         <is>
@@ -27137,7 +27137,7 @@
       </c>
       <c r="Z252" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA252" t="inlineStr">
@@ -27147,12 +27147,7 @@
       </c>
       <c r="AB252" t="inlineStr">
         <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AC252" t="inlineStr">
-        <is>
-          <t>Färsk spillning, tupp</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -27167,22 +27162,22 @@
       <c r="AT252" t="inlineStr"/>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>133570860</v>
+        <v>133570755</v>
       </c>
       <c r="B253" t="n">
-        <v>79952</v>
+        <v>79333</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -27190,21 +27185,21 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -27214,10 +27209,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>426896</v>
+        <v>427497</v>
       </c>
       <c r="R253" t="n">
-        <v>6798604</v>
+        <v>6798611</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -27249,7 +27244,7 @@
       </c>
       <c r="Z253" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA253" t="inlineStr">
@@ -27259,7 +27254,7 @@
       </c>
       <c r="AB253" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -27286,7 +27281,7 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>133570755</v>
+        <v>133570751</v>
       </c>
       <c r="B254" t="n">
         <v>79333</v>
@@ -27321,10 +27316,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>427497</v>
+        <v>427436</v>
       </c>
       <c r="R254" t="n">
-        <v>6798611</v>
+        <v>6798575</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -27356,7 +27351,7 @@
       </c>
       <c r="Z254" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA254" t="inlineStr">
@@ -27366,7 +27361,7 @@
       </c>
       <c r="AB254" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -27393,32 +27388,32 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>133570751</v>
+        <v>133570335</v>
       </c>
       <c r="B255" t="n">
-        <v>79333</v>
+        <v>57145</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
@@ -27428,13 +27423,13 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>427436</v>
+        <v>427278</v>
       </c>
       <c r="R255" t="n">
-        <v>6798575</v>
+        <v>6798720</v>
       </c>
       <c r="S255" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="T255" t="inlineStr">
         <is>
@@ -27463,7 +27458,7 @@
       </c>
       <c r="Z255" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA255" t="inlineStr">
@@ -27473,7 +27468,12 @@
       </c>
       <c r="AB255" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AC255" t="inlineStr">
+        <is>
+          <t>Färsk spillning, tupp</t>
         </is>
       </c>
       <c r="AD255" t="b">
@@ -27488,65 +27488,60 @@
       <c r="AT255" t="inlineStr"/>
       <c r="AW255" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>133570774</v>
+        <v>133570341</v>
       </c>
       <c r="B256" t="n">
-        <v>57145</v>
+        <v>79333</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
-      <c r="M256" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P256" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>427308</v>
+        <v>427374</v>
       </c>
       <c r="R256" t="n">
-        <v>6798483</v>
+        <v>6798672</v>
       </c>
       <c r="S256" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T256" t="inlineStr">
         <is>
@@ -27575,7 +27570,7 @@
       </c>
       <c r="Z256" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA256" t="inlineStr">
@@ -27585,7 +27580,7 @@
       </c>
       <c r="AB256" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD256" t="b">
@@ -27600,19 +27595,19 @@
       <c r="AT256" t="inlineStr"/>
       <c r="AW256" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>133570341</v>
+        <v>133570733</v>
       </c>
       <c r="B257" t="n">
         <v>79333</v>
@@ -27647,13 +27642,13 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>427374</v>
+        <v>427626</v>
       </c>
       <c r="R257" t="n">
-        <v>6798672</v>
+        <v>6798413</v>
       </c>
       <c r="S257" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T257" t="inlineStr">
         <is>
@@ -27682,7 +27677,7 @@
       </c>
       <c r="Z257" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA257" t="inlineStr">
@@ -27692,7 +27687,7 @@
       </c>
       <c r="AB257" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD257" t="b">
@@ -27707,19 +27702,19 @@
       <c r="AT257" t="inlineStr"/>
       <c r="AW257" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>133570733</v>
+        <v>133570345</v>
       </c>
       <c r="B258" t="n">
         <v>79333</v>
@@ -27748,19 +27743,22 @@
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
+      <c r="J258" t="inlineStr"/>
+      <c r="K258" t="inlineStr"/>
+      <c r="N258" t="inlineStr"/>
       <c r="P258" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>427626</v>
+        <v>427484</v>
       </c>
       <c r="R258" t="n">
-        <v>6798413</v>
+        <v>6798636</v>
       </c>
       <c r="S258" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T258" t="inlineStr">
         <is>
@@ -27789,7 +27787,7 @@
       </c>
       <c r="Z258" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA258" t="inlineStr">
@@ -27799,7 +27797,7 @@
       </c>
       <c r="AB258" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD258" t="b">
@@ -27808,28 +27806,29 @@
       <c r="AE258" t="b">
         <v>0</v>
       </c>
+      <c r="AF258" t="inlineStr"/>
       <c r="AG258" t="b">
         <v>0</v>
       </c>
       <c r="AT258" t="inlineStr"/>
       <c r="AW258" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>133570345</v>
+        <v>133570820</v>
       </c>
       <c r="B259" t="n">
-        <v>79333</v>
+        <v>79952</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -27837,40 +27836,37 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
-      <c r="J259" t="inlineStr"/>
-      <c r="K259" t="inlineStr"/>
-      <c r="N259" t="inlineStr"/>
       <c r="P259" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>427484</v>
+        <v>426853</v>
       </c>
       <c r="R259" t="n">
-        <v>6798636</v>
+        <v>6798894</v>
       </c>
       <c r="S259" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T259" t="inlineStr">
         <is>
@@ -27899,7 +27895,7 @@
       </c>
       <c r="Z259" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA259" t="inlineStr">
@@ -27909,7 +27905,7 @@
       </c>
       <c r="AB259" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD259" t="b">
@@ -27918,26 +27914,25 @@
       <c r="AE259" t="b">
         <v>0</v>
       </c>
-      <c r="AF259" t="inlineStr"/>
       <c r="AG259" t="b">
         <v>0</v>
       </c>
       <c r="AT259" t="inlineStr"/>
       <c r="AW259" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>133570779</v>
+        <v>133570774</v>
       </c>
       <c r="B260" t="n">
         <v>57145</v>
@@ -27966,24 +27961,21 @@
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
-      <c r="K260" t="inlineStr"/>
-      <c r="L260" t="inlineStr"/>
       <c r="M260" t="inlineStr">
         <is>
           <t>färsk spillning</t>
         </is>
       </c>
-      <c r="N260" t="inlineStr"/>
       <c r="P260" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>427247</v>
+        <v>427308</v>
       </c>
       <c r="R260" t="n">
-        <v>6798484</v>
+        <v>6798483</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -28015,7 +28007,7 @@
       </c>
       <c r="Z260" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA260" t="inlineStr">
@@ -28025,7 +28017,7 @@
       </c>
       <c r="AB260" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD260" t="b">
@@ -28052,45 +28044,53 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>133570820</v>
+        <v>133570779</v>
       </c>
       <c r="B261" t="n">
-        <v>79952</v>
+        <v>57145</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
+      <c r="K261" t="inlineStr"/>
+      <c r="L261" t="inlineStr"/>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N261" t="inlineStr"/>
       <c r="P261" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>426853</v>
+        <v>427247</v>
       </c>
       <c r="R261" t="n">
-        <v>6798894</v>
+        <v>6798484</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -28122,7 +28122,7 @@
       </c>
       <c r="Z261" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA261" t="inlineStr">
@@ -28132,7 +28132,7 @@
       </c>
       <c r="AB261" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD261" t="b">
@@ -28480,55 +28480,48 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>133570818</v>
+        <v>133570346</v>
       </c>
       <c r="B265" t="n">
-        <v>93206</v>
+        <v>79333</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I265" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J265" t="inlineStr"/>
-      <c r="K265" t="inlineStr"/>
-      <c r="N265" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr"/>
       <c r="P265" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>426852</v>
+        <v>427507</v>
       </c>
       <c r="R265" t="n">
-        <v>6798897</v>
+        <v>6798599</v>
       </c>
       <c r="S265" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T265" t="inlineStr">
         <is>
@@ -28557,7 +28550,7 @@
       </c>
       <c r="Z265" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA265" t="inlineStr">
@@ -28567,7 +28560,7 @@
       </c>
       <c r="AB265" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD265" t="b">
@@ -28576,29 +28569,28 @@
       <c r="AE265" t="b">
         <v>0</v>
       </c>
-      <c r="AF265" t="inlineStr"/>
       <c r="AG265" t="b">
         <v>0</v>
       </c>
       <c r="AT265" t="inlineStr"/>
       <c r="AW265" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>133570346</v>
+        <v>133570857</v>
       </c>
       <c r="B266" t="n">
-        <v>79333</v>
+        <v>79090</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -28606,21 +28598,21 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
@@ -28630,13 +28622,13 @@
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>427507</v>
+        <v>426896</v>
       </c>
       <c r="R266" t="n">
-        <v>6798599</v>
+        <v>6798620</v>
       </c>
       <c r="S266" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T266" t="inlineStr">
         <is>
@@ -28665,7 +28657,7 @@
       </c>
       <c r="Z266" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA266" t="inlineStr">
@@ -28675,7 +28667,7 @@
       </c>
       <c r="AB266" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD266" t="b">
@@ -28690,22 +28682,22 @@
       <c r="AT266" t="inlineStr"/>
       <c r="AW266" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX266" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>133570336</v>
+        <v>133570769</v>
       </c>
       <c r="B267" t="n">
-        <v>57955</v>
+        <v>79333</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -28713,21 +28705,21 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
@@ -28737,13 +28729,13 @@
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>427282</v>
+        <v>427309</v>
       </c>
       <c r="R267" t="n">
-        <v>6798727</v>
+        <v>6798726</v>
       </c>
       <c r="S267" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T267" t="inlineStr">
         <is>
@@ -28772,7 +28764,7 @@
       </c>
       <c r="Z267" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA267" t="inlineStr">
@@ -28782,12 +28774,7 @@
       </c>
       <c r="AB267" t="inlineStr">
         <is>
-          <t>13:17</t>
-        </is>
-      </c>
-      <c r="AC267" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD267" t="b">
@@ -28802,57 +28789,62 @@
       <c r="AT267" t="inlineStr"/>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>133570857</v>
+        <v>133570758</v>
       </c>
       <c r="B268" t="n">
-        <v>79090</v>
+        <v>57145</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P268" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>426896</v>
+        <v>427432</v>
       </c>
       <c r="R268" t="n">
-        <v>6798620</v>
+        <v>6798638</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -28884,7 +28876,7 @@
       </c>
       <c r="Z268" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA268" t="inlineStr">
@@ -28894,7 +28886,7 @@
       </c>
       <c r="AB268" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD268" t="b">
@@ -28921,45 +28913,52 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>133570769</v>
+        <v>133570818</v>
       </c>
       <c r="B269" t="n">
-        <v>79333</v>
+        <v>93206</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I269" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr"/>
+      <c r="K269" t="inlineStr"/>
+      <c r="N269" t="inlineStr"/>
       <c r="P269" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>427309</v>
+        <v>426852</v>
       </c>
       <c r="R269" t="n">
-        <v>6798726</v>
+        <v>6798897</v>
       </c>
       <c r="S269" t="n">
         <v>10</v>
@@ -28991,7 +28990,7 @@
       </c>
       <c r="Z269" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA269" t="inlineStr">
@@ -29001,7 +29000,7 @@
       </c>
       <c r="AB269" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD269" t="b">
@@ -29010,6 +29009,7 @@
       <c r="AE269" t="b">
         <v>0</v>
       </c>
+      <c r="AF269" t="inlineStr"/>
       <c r="AG269" t="b">
         <v>0</v>
       </c>
@@ -29028,53 +29028,48 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>133570758</v>
+        <v>133570336</v>
       </c>
       <c r="B270" t="n">
-        <v>57145</v>
+        <v>57955</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E270" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
-      <c r="M270" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P270" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>427432</v>
+        <v>427282</v>
       </c>
       <c r="R270" t="n">
-        <v>6798638</v>
+        <v>6798727</v>
       </c>
       <c r="S270" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T270" t="inlineStr">
         <is>
@@ -29103,7 +29098,7 @@
       </c>
       <c r="Z270" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA270" t="inlineStr">
@@ -29113,7 +29108,12 @@
       </c>
       <c r="AB270" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AC270" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD270" t="b">
@@ -29128,60 +29128,63 @@
       <c r="AT270" t="inlineStr"/>
       <c r="AW270" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>133570329</v>
+        <v>133570850</v>
       </c>
       <c r="B271" t="n">
-        <v>57145</v>
+        <v>79952</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E271" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
+      <c r="J271" t="inlineStr"/>
+      <c r="K271" t="inlineStr"/>
+      <c r="N271" t="inlineStr"/>
       <c r="P271" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>427281</v>
+        <v>426946</v>
       </c>
       <c r="R271" t="n">
-        <v>6798466</v>
+        <v>6798659</v>
       </c>
       <c r="S271" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T271" t="inlineStr">
         <is>
@@ -29210,7 +29213,7 @@
       </c>
       <c r="Z271" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA271" t="inlineStr">
@@ -29220,12 +29223,7 @@
       </c>
       <c r="AB271" t="inlineStr">
         <is>
-          <t>12:47</t>
-        </is>
-      </c>
-      <c r="AC271" t="inlineStr">
-        <is>
-          <t>Färsk spillning höna</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AD271" t="b">
@@ -29234,56 +29232,57 @@
       <c r="AE271" t="b">
         <v>0</v>
       </c>
+      <c r="AF271" t="inlineStr"/>
       <c r="AG271" t="b">
         <v>0</v>
       </c>
       <c r="AT271" t="inlineStr"/>
       <c r="AW271" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX271" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>133570742</v>
+        <v>133570817</v>
       </c>
       <c r="B272" t="n">
-        <v>57145</v>
+        <v>57955</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
       <c r="M272" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P272" t="inlineStr">
@@ -29292,10 +29291,10 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>427499</v>
+        <v>426860</v>
       </c>
       <c r="R272" t="n">
-        <v>6798481</v>
+        <v>6798955</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -29327,7 +29326,7 @@
       </c>
       <c r="Z272" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA272" t="inlineStr">
@@ -29337,7 +29336,7 @@
       </c>
       <c r="AB272" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD272" t="b">
@@ -29364,7 +29363,7 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>133570817</v>
+        <v>133570765</v>
       </c>
       <c r="B273" t="n">
         <v>57955</v>
@@ -29395,7 +29394,7 @@
       <c r="I273" t="inlineStr"/>
       <c r="M273" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P273" t="inlineStr">
@@ -29404,10 +29403,10 @@
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>426860</v>
+        <v>427230</v>
       </c>
       <c r="R273" t="n">
-        <v>6798955</v>
+        <v>6798732</v>
       </c>
       <c r="S273" t="n">
         <v>10</v>
@@ -29439,7 +29438,7 @@
       </c>
       <c r="Z273" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA273" t="inlineStr">
@@ -29449,7 +29448,7 @@
       </c>
       <c r="AB273" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD273" t="b">
@@ -29476,38 +29475,38 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>133570765</v>
+        <v>133570742</v>
       </c>
       <c r="B274" t="n">
-        <v>57955</v>
+        <v>57145</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
       <c r="M274" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P274" t="inlineStr">
@@ -29516,10 +29515,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>427230</v>
+        <v>427499</v>
       </c>
       <c r="R274" t="n">
-        <v>6798732</v>
+        <v>6798481</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -29551,7 +29550,7 @@
       </c>
       <c r="Z274" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA274" t="inlineStr">
@@ -29561,7 +29560,7 @@
       </c>
       <c r="AB274" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD274" t="b">
@@ -29588,51 +29587,48 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>133570850</v>
+        <v>133570329</v>
       </c>
       <c r="B275" t="n">
-        <v>79952</v>
+        <v>57145</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
-      <c r="J275" t="inlineStr"/>
-      <c r="K275" t="inlineStr"/>
-      <c r="N275" t="inlineStr"/>
       <c r="P275" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>426946</v>
+        <v>427281</v>
       </c>
       <c r="R275" t="n">
-        <v>6798659</v>
+        <v>6798466</v>
       </c>
       <c r="S275" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T275" t="inlineStr">
         <is>
@@ -29661,7 +29657,7 @@
       </c>
       <c r="Z275" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA275" t="inlineStr">
@@ -29671,7 +29667,12 @@
       </c>
       <c r="AB275" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AC275" t="inlineStr">
+        <is>
+          <t>Färsk spillning höna</t>
         </is>
       </c>
       <c r="AD275" t="b">
@@ -29680,29 +29681,28 @@
       <c r="AE275" t="b">
         <v>0</v>
       </c>
-      <c r="AF275" t="inlineStr"/>
       <c r="AG275" t="b">
         <v>0</v>
       </c>
       <c r="AT275" t="inlineStr"/>
       <c r="AW275" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX275" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>133570749</v>
+        <v>133570862</v>
       </c>
       <c r="B276" t="n">
-        <v>57955</v>
+        <v>79952</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -29710,39 +29710,34 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
-      <c r="M276" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P276" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>427437</v>
+        <v>426896</v>
       </c>
       <c r="R276" t="n">
-        <v>6798580</v>
+        <v>6798605</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -29774,7 +29769,7 @@
       </c>
       <c r="Z276" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA276" t="inlineStr">
@@ -29784,7 +29779,7 @@
       </c>
       <c r="AB276" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD276" t="b">
@@ -29811,32 +29806,32 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>133570731</v>
+        <v>133570340</v>
       </c>
       <c r="B277" t="n">
-        <v>106243</v>
+        <v>79090</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E277" t="n">
-        <v>221725</v>
+        <v>6446</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I277" t="inlineStr"/>
@@ -29846,13 +29841,13 @@
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>427595</v>
+        <v>427316</v>
       </c>
       <c r="R277" t="n">
-        <v>6798440</v>
+        <v>6798744</v>
       </c>
       <c r="S277" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T277" t="inlineStr">
         <is>
@@ -29881,7 +29876,7 @@
       </c>
       <c r="Z277" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA277" t="inlineStr">
@@ -29891,7 +29886,7 @@
       </c>
       <c r="AB277" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD277" t="b">
@@ -29906,22 +29901,22 @@
       <c r="AT277" t="inlineStr"/>
       <c r="AW277" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX277" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>133570760</v>
+        <v>133570768</v>
       </c>
       <c r="B278" t="n">
-        <v>57955</v>
+        <v>79333</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -29929,39 +29924,34 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
-      <c r="M278" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P278" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>427373</v>
+        <v>427280</v>
       </c>
       <c r="R278" t="n">
-        <v>6798670</v>
+        <v>6798731</v>
       </c>
       <c r="S278" t="n">
         <v>10</v>
@@ -29993,7 +29983,7 @@
       </c>
       <c r="Z278" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA278" t="inlineStr">
@@ -30003,7 +29993,7 @@
       </c>
       <c r="AB278" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD278" t="b">
@@ -30030,10 +30020,10 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>133570862</v>
+        <v>133570760</v>
       </c>
       <c r="B279" t="n">
-        <v>79952</v>
+        <v>57955</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -30041,34 +30031,39 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P279" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>426896</v>
+        <v>427373</v>
       </c>
       <c r="R279" t="n">
-        <v>6798605</v>
+        <v>6798670</v>
       </c>
       <c r="S279" t="n">
         <v>10</v>
@@ -30100,7 +30095,7 @@
       </c>
       <c r="Z279" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA279" t="inlineStr">
@@ -30110,7 +30105,7 @@
       </c>
       <c r="AB279" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD279" t="b">
@@ -30585,10 +30580,10 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>133570340</v>
+        <v>133570749</v>
       </c>
       <c r="B284" t="n">
-        <v>79090</v>
+        <v>57955</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -30596,37 +30591,42 @@
         </is>
       </c>
       <c r="E284" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I284" t="inlineStr"/>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P284" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>427316</v>
+        <v>427437</v>
       </c>
       <c r="R284" t="n">
-        <v>6798744</v>
+        <v>6798580</v>
       </c>
       <c r="S284" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T284" t="inlineStr">
         <is>
@@ -30655,7 +30655,7 @@
       </c>
       <c r="Z284" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA284" t="inlineStr">
@@ -30665,7 +30665,7 @@
       </c>
       <c r="AB284" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD284" t="b">
@@ -30680,12 +30680,12 @@
       <c r="AT284" t="inlineStr"/>
       <c r="AW284" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX284" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY284" t="inlineStr"/>
@@ -30911,32 +30911,32 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>133570768</v>
+        <v>133570731</v>
       </c>
       <c r="B287" t="n">
-        <v>79333</v>
+        <v>106243</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E287" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I287" t="inlineStr"/>
@@ -30946,10 +30946,10 @@
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>427280</v>
+        <v>427595</v>
       </c>
       <c r="R287" t="n">
-        <v>6798731</v>
+        <v>6798440</v>
       </c>
       <c r="S287" t="n">
         <v>10</v>
@@ -30981,7 +30981,7 @@
       </c>
       <c r="Z287" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA287" t="inlineStr">
@@ -30991,7 +30991,7 @@
       </c>
       <c r="AB287" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD287" t="b">
@@ -31018,27 +31018,27 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>133570330</v>
+        <v>133570762</v>
       </c>
       <c r="B288" t="n">
-        <v>57145</v>
+        <v>56522</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E288" t="n">
-        <v>100138</v>
+        <v>206004</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -31047,19 +31047,24 @@
         </is>
       </c>
       <c r="I288" t="inlineStr"/>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P288" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q288" t="n">
-        <v>427301</v>
+        <v>427205</v>
       </c>
       <c r="R288" t="n">
-        <v>6798481</v>
+        <v>6798756</v>
       </c>
       <c r="S288" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T288" t="inlineStr">
         <is>
@@ -31088,7 +31093,7 @@
       </c>
       <c r="Z288" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA288" t="inlineStr">
@@ -31098,12 +31103,7 @@
       </c>
       <c r="AB288" t="inlineStr">
         <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC288" t="inlineStr">
-        <is>
-          <t>Färsk spillning, tupp</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD288" t="b">
@@ -31118,22 +31118,22 @@
       <c r="AT288" t="inlineStr"/>
       <c r="AW288" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX288" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>133570762</v>
+        <v>133570362</v>
       </c>
       <c r="B289" t="n">
-        <v>56522</v>
+        <v>79333</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -31141,42 +31141,37 @@
         </is>
       </c>
       <c r="E289" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I289" t="inlineStr"/>
-      <c r="M289" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P289" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q289" t="n">
-        <v>427205</v>
+        <v>427452</v>
       </c>
       <c r="R289" t="n">
-        <v>6798756</v>
+        <v>6798410</v>
       </c>
       <c r="S289" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T289" t="inlineStr">
         <is>
@@ -31205,7 +31200,7 @@
       </c>
       <c r="Z289" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA289" t="inlineStr">
@@ -31215,7 +31210,7 @@
       </c>
       <c r="AB289" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD289" t="b">
@@ -31230,44 +31225,44 @@
       <c r="AT289" t="inlineStr"/>
       <c r="AW289" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX289" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>133570362</v>
+        <v>133570330</v>
       </c>
       <c r="B290" t="n">
-        <v>79333</v>
+        <v>57145</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E290" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I290" t="inlineStr"/>
@@ -31277,10 +31272,10 @@
         </is>
       </c>
       <c r="Q290" t="n">
-        <v>427452</v>
+        <v>427301</v>
       </c>
       <c r="R290" t="n">
-        <v>6798410</v>
+        <v>6798481</v>
       </c>
       <c r="S290" t="n">
         <v>5</v>
@@ -31312,7 +31307,7 @@
       </c>
       <c r="Z290" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA290" t="inlineStr">
@@ -31322,7 +31317,12 @@
       </c>
       <c r="AB290" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC290" t="inlineStr">
+        <is>
+          <t>Färsk spillning, tupp</t>
         </is>
       </c>
       <c r="AD290" t="b">
@@ -31563,53 +31563,45 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>133570778</v>
+        <v>133570825</v>
       </c>
       <c r="B293" t="n">
-        <v>57145</v>
+        <v>79952</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E293" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I293" t="inlineStr"/>
-      <c r="K293" t="inlineStr"/>
-      <c r="L293" t="inlineStr"/>
-      <c r="M293" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N293" t="inlineStr"/>
       <c r="P293" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q293" t="n">
-        <v>427271</v>
+        <v>426913</v>
       </c>
       <c r="R293" t="n">
-        <v>6798485</v>
+        <v>6798823</v>
       </c>
       <c r="S293" t="n">
         <v>10</v>
@@ -31641,7 +31633,7 @@
       </c>
       <c r="Z293" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA293" t="inlineStr">
@@ -31651,7 +31643,7 @@
       </c>
       <c r="AB293" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD293" t="b">
@@ -31678,10 +31670,10 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>133570771</v>
+        <v>133570325</v>
       </c>
       <c r="B294" t="n">
-        <v>57955</v>
+        <v>79090</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -31689,42 +31681,40 @@
         </is>
       </c>
       <c r="E294" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I294" t="inlineStr"/>
-      <c r="M294" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J294" t="inlineStr"/>
+      <c r="K294" t="inlineStr"/>
+      <c r="N294" t="inlineStr"/>
       <c r="P294" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q294" t="n">
-        <v>427330</v>
+        <v>427249</v>
       </c>
       <c r="R294" t="n">
-        <v>6798534</v>
+        <v>6798389</v>
       </c>
       <c r="S294" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T294" t="inlineStr">
         <is>
@@ -31753,7 +31743,7 @@
       </c>
       <c r="Z294" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA294" t="inlineStr">
@@ -31763,7 +31753,12 @@
       </c>
       <c r="AB294" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AC294" t="inlineStr">
+        <is>
+          <t>Brandstubbe</t>
         </is>
       </c>
       <c r="AD294" t="b">
@@ -31772,28 +31767,29 @@
       <c r="AE294" t="b">
         <v>0</v>
       </c>
+      <c r="AF294" t="inlineStr"/>
       <c r="AG294" t="b">
         <v>0</v>
       </c>
       <c r="AT294" t="inlineStr"/>
       <c r="AW294" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX294" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>133570825</v>
+        <v>133570842</v>
       </c>
       <c r="B295" t="n">
-        <v>79952</v>
+        <v>79090</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -31801,34 +31797,37 @@
         </is>
       </c>
       <c r="E295" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I295" t="inlineStr"/>
+      <c r="J295" t="inlineStr"/>
+      <c r="K295" t="inlineStr"/>
+      <c r="N295" t="inlineStr"/>
       <c r="P295" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q295" t="n">
-        <v>426913</v>
+        <v>426905</v>
       </c>
       <c r="R295" t="n">
-        <v>6798823</v>
+        <v>6798726</v>
       </c>
       <c r="S295" t="n">
         <v>10</v>
@@ -31860,7 +31859,7 @@
       </c>
       <c r="Z295" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA295" t="inlineStr">
@@ -31870,7 +31869,7 @@
       </c>
       <c r="AB295" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD295" t="b">
@@ -31879,6 +31878,7 @@
       <c r="AE295" t="b">
         <v>0</v>
       </c>
+      <c r="AF295" t="inlineStr"/>
       <c r="AG295" t="b">
         <v>0</v>
       </c>
@@ -31897,7 +31897,7 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>133570770</v>
+        <v>133570771</v>
       </c>
       <c r="B296" t="n">
         <v>57955</v>
@@ -31937,10 +31937,10 @@
         </is>
       </c>
       <c r="Q296" t="n">
-        <v>427326</v>
+        <v>427330</v>
       </c>
       <c r="R296" t="n">
-        <v>6798715</v>
+        <v>6798534</v>
       </c>
       <c r="S296" t="n">
         <v>10</v>
@@ -31972,7 +31972,7 @@
       </c>
       <c r="Z296" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA296" t="inlineStr">
@@ -31982,7 +31982,7 @@
       </c>
       <c r="AB296" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD296" t="b">
@@ -32009,10 +32009,10 @@
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>133570325</v>
+        <v>133570770</v>
       </c>
       <c r="B297" t="n">
-        <v>79090</v>
+        <v>57955</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -32020,40 +32020,42 @@
         </is>
       </c>
       <c r="E297" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I297" t="inlineStr"/>
-      <c r="J297" t="inlineStr"/>
-      <c r="K297" t="inlineStr"/>
-      <c r="N297" t="inlineStr"/>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P297" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q297" t="n">
-        <v>427249</v>
+        <v>427326</v>
       </c>
       <c r="R297" t="n">
-        <v>6798389</v>
+        <v>6798715</v>
       </c>
       <c r="S297" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T297" t="inlineStr">
         <is>
@@ -32082,7 +32084,7 @@
       </c>
       <c r="Z297" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA297" t="inlineStr">
@@ -32092,12 +32094,7 @@
       </c>
       <c r="AB297" t="inlineStr">
         <is>
-          <t>12:36</t>
-        </is>
-      </c>
-      <c r="AC297" t="inlineStr">
-        <is>
-          <t>Brandstubbe</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD297" t="b">
@@ -32106,56 +32103,60 @@
       <c r="AE297" t="b">
         <v>0</v>
       </c>
-      <c r="AF297" t="inlineStr"/>
       <c r="AG297" t="b">
         <v>0</v>
       </c>
       <c r="AT297" t="inlineStr"/>
       <c r="AW297" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX297" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>133570842</v>
+        <v>133570778</v>
       </c>
       <c r="B298" t="n">
-        <v>79090</v>
+        <v>57145</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E298" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I298" t="inlineStr"/>
-      <c r="J298" t="inlineStr"/>
       <c r="K298" t="inlineStr"/>
+      <c r="L298" t="inlineStr"/>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N298" t="inlineStr"/>
       <c r="P298" t="inlineStr">
         <is>
@@ -32163,10 +32164,10 @@
         </is>
       </c>
       <c r="Q298" t="n">
-        <v>426905</v>
+        <v>427271</v>
       </c>
       <c r="R298" t="n">
-        <v>6798726</v>
+        <v>6798485</v>
       </c>
       <c r="S298" t="n">
         <v>10</v>
@@ -32198,7 +32199,7 @@
       </c>
       <c r="Z298" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA298" t="inlineStr">
@@ -32208,7 +32209,7 @@
       </c>
       <c r="AB298" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD298" t="b">
@@ -32217,7 +32218,6 @@
       <c r="AE298" t="b">
         <v>0</v>
       </c>
-      <c r="AF298" t="inlineStr"/>
       <c r="AG298" t="b">
         <v>0</v>
       </c>
@@ -32236,7 +32236,7 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>133570868</v>
+        <v>133570830</v>
       </c>
       <c r="B299" t="n">
         <v>57955</v>
@@ -32267,7 +32267,7 @@
       <c r="I299" t="inlineStr"/>
       <c r="M299" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P299" t="inlineStr">
@@ -32276,10 +32276,10 @@
         </is>
       </c>
       <c r="Q299" t="n">
-        <v>426866</v>
+        <v>426912</v>
       </c>
       <c r="R299" t="n">
-        <v>6798608</v>
+        <v>6798798</v>
       </c>
       <c r="S299" t="n">
         <v>10</v>
@@ -32311,7 +32311,7 @@
       </c>
       <c r="Z299" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA299" t="inlineStr">
@@ -32321,7 +32321,12 @@
       </c>
       <c r="AB299" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC299" t="inlineStr">
+        <is>
+          <t>10.00</t>
         </is>
       </c>
       <c r="AD299" t="b">
@@ -32348,7 +32353,7 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>133570830</v>
+        <v>133570784</v>
       </c>
       <c r="B300" t="n">
         <v>57955</v>
@@ -32379,7 +32384,7 @@
       <c r="I300" t="inlineStr"/>
       <c r="M300" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P300" t="inlineStr">
@@ -32388,10 +32393,10 @@
         </is>
       </c>
       <c r="Q300" t="n">
-        <v>426912</v>
+        <v>427227</v>
       </c>
       <c r="R300" t="n">
-        <v>6798798</v>
+        <v>6798423</v>
       </c>
       <c r="S300" t="n">
         <v>10</v>
@@ -32423,7 +32428,7 @@
       </c>
       <c r="Z300" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA300" t="inlineStr">
@@ -32433,12 +32438,7 @@
       </c>
       <c r="AB300" t="inlineStr">
         <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="AC300" t="inlineStr">
-        <is>
-          <t>10.00</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD300" t="b">
@@ -32465,7 +32465,7 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>133570784</v>
+        <v>133570868</v>
       </c>
       <c r="B301" t="n">
         <v>57955</v>
@@ -32505,10 +32505,10 @@
         </is>
       </c>
       <c r="Q301" t="n">
-        <v>427227</v>
+        <v>426866</v>
       </c>
       <c r="R301" t="n">
-        <v>6798423</v>
+        <v>6798608</v>
       </c>
       <c r="S301" t="n">
         <v>10</v>
@@ -32540,7 +32540,7 @@
       </c>
       <c r="Z301" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA301" t="inlineStr">
@@ -32550,7 +32550,7 @@
       </c>
       <c r="AB301" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD301" t="b">
@@ -32577,10 +32577,10 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>133570780</v>
+        <v>133570865</v>
       </c>
       <c r="B302" t="n">
-        <v>79952</v>
+        <v>79091</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -32588,21 +32588,21 @@
         </is>
       </c>
       <c r="E302" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I302" t="inlineStr"/>
@@ -32612,10 +32612,10 @@
         </is>
       </c>
       <c r="Q302" t="n">
-        <v>427229</v>
+        <v>426873</v>
       </c>
       <c r="R302" t="n">
-        <v>6798492</v>
+        <v>6798607</v>
       </c>
       <c r="S302" t="n">
         <v>10</v>
@@ -32647,7 +32647,7 @@
       </c>
       <c r="Z302" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA302" t="inlineStr">
@@ -32657,7 +32657,7 @@
       </c>
       <c r="AB302" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AD302" t="b">
@@ -32684,10 +32684,10 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>133570351</v>
+        <v>133570780</v>
       </c>
       <c r="B303" t="n">
-        <v>79333</v>
+        <v>79952</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -32695,21 +32695,21 @@
         </is>
       </c>
       <c r="E303" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I303" t="inlineStr"/>
@@ -32719,13 +32719,13 @@
         </is>
       </c>
       <c r="Q303" t="n">
-        <v>427528</v>
+        <v>427229</v>
       </c>
       <c r="R303" t="n">
-        <v>6798510</v>
+        <v>6798492</v>
       </c>
       <c r="S303" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T303" t="inlineStr">
         <is>
@@ -32754,7 +32754,7 @@
       </c>
       <c r="Z303" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA303" t="inlineStr">
@@ -32764,7 +32764,7 @@
       </c>
       <c r="AB303" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD303" t="b">
@@ -32779,19 +32779,19 @@
       <c r="AT303" t="inlineStr"/>
       <c r="AW303" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX303" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>133570350</v>
+        <v>133570351</v>
       </c>
       <c r="B304" t="n">
         <v>79333</v>
@@ -32826,13 +32826,13 @@
         </is>
       </c>
       <c r="Q304" t="n">
-        <v>427523</v>
+        <v>427528</v>
       </c>
       <c r="R304" t="n">
-        <v>6798536</v>
+        <v>6798510</v>
       </c>
       <c r="S304" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="T304" t="inlineStr">
         <is>
@@ -32861,7 +32861,7 @@
       </c>
       <c r="Z304" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA304" t="inlineStr">
@@ -32871,7 +32871,7 @@
       </c>
       <c r="AB304" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD304" t="b">
@@ -32898,10 +32898,10 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>133570865</v>
+        <v>133570350</v>
       </c>
       <c r="B305" t="n">
-        <v>79091</v>
+        <v>79333</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -32909,21 +32909,21 @@
         </is>
       </c>
       <c r="E305" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I305" t="inlineStr"/>
@@ -32933,13 +32933,13 @@
         </is>
       </c>
       <c r="Q305" t="n">
-        <v>426873</v>
+        <v>427523</v>
       </c>
       <c r="R305" t="n">
-        <v>6798607</v>
+        <v>6798536</v>
       </c>
       <c r="S305" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="T305" t="inlineStr">
         <is>
@@ -32968,7 +32968,7 @@
       </c>
       <c r="Z305" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA305" t="inlineStr">
@@ -32978,7 +32978,7 @@
       </c>
       <c r="AB305" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD305" t="b">
@@ -32993,12 +32993,12 @@
       <c r="AT305" t="inlineStr"/>
       <c r="AW305" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX305" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY305" t="inlineStr"/>
@@ -33219,32 +33219,32 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>133570331</v>
+        <v>133570348</v>
       </c>
       <c r="B308" t="n">
-        <v>57145</v>
+        <v>79333</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E308" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I308" t="inlineStr"/>
@@ -33254,10 +33254,10 @@
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>427300</v>
+        <v>427509</v>
       </c>
       <c r="R308" t="n">
-        <v>6798486</v>
+        <v>6798594</v>
       </c>
       <c r="S308" t="n">
         <v>5</v>
@@ -33289,7 +33289,7 @@
       </c>
       <c r="Z308" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA308" t="inlineStr">
@@ -33299,12 +33299,7 @@
       </c>
       <c r="AB308" t="inlineStr">
         <is>
-          <t>12:53</t>
-        </is>
-      </c>
-      <c r="AC308" t="inlineStr">
-        <is>
-          <t>Färsk spillning, tupp</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD308" t="b">
@@ -33331,10 +33326,10 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>133570348</v>
+        <v>133570761</v>
       </c>
       <c r="B309" t="n">
-        <v>79333</v>
+        <v>79952</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -33342,21 +33337,21 @@
         </is>
       </c>
       <c r="E309" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I309" t="inlineStr"/>
@@ -33366,13 +33361,13 @@
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>427509</v>
+        <v>427305</v>
       </c>
       <c r="R309" t="n">
-        <v>6798594</v>
+        <v>6798750</v>
       </c>
       <c r="S309" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T309" t="inlineStr">
         <is>
@@ -33401,7 +33396,7 @@
       </c>
       <c r="Z309" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA309" t="inlineStr">
@@ -33411,7 +33406,7 @@
       </c>
       <c r="AB309" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD309" t="b">
@@ -33426,44 +33421,44 @@
       <c r="AT309" t="inlineStr"/>
       <c r="AW309" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX309" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>133570314</v>
+        <v>133570331</v>
       </c>
       <c r="B310" t="n">
-        <v>79923</v>
+        <v>57145</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E310" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I310" t="inlineStr"/>
@@ -33473,10 +33468,10 @@
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>426883</v>
+        <v>427300</v>
       </c>
       <c r="R310" t="n">
-        <v>6798845</v>
+        <v>6798486</v>
       </c>
       <c r="S310" t="n">
         <v>5</v>
@@ -33508,7 +33503,7 @@
       </c>
       <c r="Z310" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA310" t="inlineStr">
@@ -33518,12 +33513,12 @@
       </c>
       <c r="AB310" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AC310" t="inlineStr">
         <is>
-          <t>Äldre rotvälta</t>
+          <t>Färsk spillning, tupp</t>
         </is>
       </c>
       <c r="AD310" t="b">
@@ -33550,10 +33545,10 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>133570761</v>
+        <v>133570314</v>
       </c>
       <c r="B311" t="n">
-        <v>79952</v>
+        <v>79923</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -33561,21 +33556,21 @@
         </is>
       </c>
       <c r="E311" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I311" t="inlineStr"/>
@@ -33585,13 +33580,13 @@
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>427305</v>
+        <v>426883</v>
       </c>
       <c r="R311" t="n">
-        <v>6798750</v>
+        <v>6798845</v>
       </c>
       <c r="S311" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T311" t="inlineStr">
         <is>
@@ -33620,7 +33615,7 @@
       </c>
       <c r="Z311" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA311" t="inlineStr">
@@ -33630,7 +33625,12 @@
       </c>
       <c r="AB311" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AC311" t="inlineStr">
+        <is>
+          <t>Äldre rotvälta</t>
         </is>
       </c>
       <c r="AD311" t="b">
@@ -33645,44 +33645,44 @@
       <c r="AT311" t="inlineStr"/>
       <c r="AW311" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX311" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>133570337</v>
+        <v>133570754</v>
       </c>
       <c r="B312" t="n">
-        <v>79333</v>
+        <v>98001</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E312" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I312" t="inlineStr"/>
@@ -33692,13 +33692,13 @@
         </is>
       </c>
       <c r="Q312" t="n">
-        <v>427280</v>
+        <v>427512</v>
       </c>
       <c r="R312" t="n">
-        <v>6798728</v>
+        <v>6798623</v>
       </c>
       <c r="S312" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T312" t="inlineStr">
         <is>
@@ -33727,7 +33727,7 @@
       </c>
       <c r="Z312" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA312" t="inlineStr">
@@ -33737,7 +33737,7 @@
       </c>
       <c r="AB312" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD312" t="b">
@@ -33752,44 +33752,44 @@
       <c r="AT312" t="inlineStr"/>
       <c r="AW312" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX312" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>133570754</v>
+        <v>133570744</v>
       </c>
       <c r="B313" t="n">
-        <v>98001</v>
+        <v>79090</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E313" t="n">
-        <v>221941</v>
+        <v>6446</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I313" t="inlineStr"/>
@@ -33799,10 +33799,10 @@
         </is>
       </c>
       <c r="Q313" t="n">
-        <v>427512</v>
+        <v>427459</v>
       </c>
       <c r="R313" t="n">
-        <v>6798623</v>
+        <v>6798536</v>
       </c>
       <c r="S313" t="n">
         <v>10</v>
@@ -33834,7 +33834,7 @@
       </c>
       <c r="Z313" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA313" t="inlineStr">
@@ -33844,7 +33844,7 @@
       </c>
       <c r="AB313" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD313" t="b">
@@ -33871,10 +33871,10 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>133570843</v>
+        <v>133570337</v>
       </c>
       <c r="B314" t="n">
-        <v>58119</v>
+        <v>79333</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -33882,45 +33882,37 @@
         </is>
       </c>
       <c r="E314" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I314" t="inlineStr"/>
-      <c r="K314" t="inlineStr"/>
-      <c r="L314" t="inlineStr"/>
-      <c r="M314" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N314" t="inlineStr"/>
       <c r="P314" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q314" t="n">
-        <v>426918</v>
+        <v>427280</v>
       </c>
       <c r="R314" t="n">
-        <v>6798710</v>
+        <v>6798728</v>
       </c>
       <c r="S314" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T314" t="inlineStr">
         <is>
@@ -33949,7 +33941,7 @@
       </c>
       <c r="Z314" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA314" t="inlineStr">
@@ -33959,7 +33951,7 @@
       </c>
       <c r="AB314" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD314" t="b">
@@ -33974,22 +33966,22 @@
       <c r="AT314" t="inlineStr"/>
       <c r="AW314" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX314" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>133570744</v>
+        <v>133570855</v>
       </c>
       <c r="B315" t="n">
-        <v>79090</v>
+        <v>79952</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -33997,21 +33989,21 @@
         </is>
       </c>
       <c r="E315" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I315" t="inlineStr"/>
@@ -34021,10 +34013,10 @@
         </is>
       </c>
       <c r="Q315" t="n">
-        <v>427459</v>
+        <v>426909</v>
       </c>
       <c r="R315" t="n">
-        <v>6798536</v>
+        <v>6798629</v>
       </c>
       <c r="S315" t="n">
         <v>10</v>
@@ -34056,7 +34048,7 @@
       </c>
       <c r="Z315" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA315" t="inlineStr">
@@ -34066,7 +34058,7 @@
       </c>
       <c r="AB315" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD315" t="b">
@@ -34093,10 +34085,10 @@
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>133570855</v>
+        <v>133570843</v>
       </c>
       <c r="B316" t="n">
-        <v>79952</v>
+        <v>58119</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -34104,34 +34096,42 @@
         </is>
       </c>
       <c r="E316" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I316" t="inlineStr"/>
+      <c r="K316" t="inlineStr"/>
+      <c r="L316" t="inlineStr"/>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N316" t="inlineStr"/>
       <c r="P316" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q316" t="n">
-        <v>426909</v>
+        <v>426918</v>
       </c>
       <c r="R316" t="n">
-        <v>6798629</v>
+        <v>6798710</v>
       </c>
       <c r="S316" t="n">
         <v>10</v>
@@ -34163,7 +34163,7 @@
       </c>
       <c r="Z316" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA316" t="inlineStr">
@@ -34173,7 +34173,7 @@
       </c>
       <c r="AB316" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD316" t="b">

--- a/artfynd/A 4832-2026 artfynd.xlsx
+++ b/artfynd/A 4832-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY316"/>
+  <dimension ref="A1:AY322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1466,10 +1466,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133570794</v>
+        <v>133570813</v>
       </c>
       <c r="B10" t="n">
-        <v>79091</v>
+        <v>79952</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1477,37 +1477,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>426789</v>
+        <v>426823</v>
       </c>
       <c r="R10" t="n">
-        <v>6798764</v>
+        <v>6799024</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1539,7 +1536,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1549,7 +1546,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1558,7 +1555,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1577,10 +1573,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133570813</v>
+        <v>133570794</v>
       </c>
       <c r="B11" t="n">
-        <v>79952</v>
+        <v>79091</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1588,34 +1584,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>426823</v>
+        <v>426789</v>
       </c>
       <c r="R11" t="n">
-        <v>6799024</v>
+        <v>6798764</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1647,7 +1646,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1657,7 +1656,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1666,6 +1665,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -4075,10 +4075,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133570320</v>
+        <v>133570318</v>
       </c>
       <c r="B34" t="n">
-        <v>79091</v>
+        <v>79952</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4086,37 +4086,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>426770</v>
+        <v>426768</v>
       </c>
       <c r="R34" t="n">
-        <v>6798688</v>
+        <v>6798900</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4148,7 +4145,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4158,7 +4155,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Brandstubbe</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4167,7 +4169,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4186,7 +4187,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133570318</v>
+        <v>133570791</v>
       </c>
       <c r="B35" t="n">
         <v>79952</v>
@@ -4215,19 +4216,22 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>426768</v>
+        <v>426773</v>
       </c>
       <c r="R35" t="n">
-        <v>6798900</v>
+        <v>6798682</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4256,7 +4260,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4266,12 +4270,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Brandstubbe</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4280,28 +4279,29 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133570791</v>
+        <v>133570788</v>
       </c>
       <c r="B36" t="n">
-        <v>79952</v>
+        <v>79090</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4309,37 +4309,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>426773</v>
+        <v>426784</v>
       </c>
       <c r="R36" t="n">
-        <v>6798682</v>
+        <v>6798588</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4371,7 +4368,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4381,7 +4378,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4390,7 +4387,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4409,10 +4405,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133570788</v>
+        <v>133570315</v>
       </c>
       <c r="B37" t="n">
-        <v>79090</v>
+        <v>79952</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4420,21 +4416,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4444,13 +4440,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>426784</v>
+        <v>426759</v>
       </c>
       <c r="R37" t="n">
-        <v>6798588</v>
+        <v>6799090</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4479,7 +4475,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4489,7 +4485,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Äldre stubbe</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4504,22 +4505,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133570315</v>
+        <v>133570320</v>
       </c>
       <c r="B38" t="n">
-        <v>79952</v>
+        <v>79091</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4527,34 +4528,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>426759</v>
+        <v>426770</v>
       </c>
       <c r="R38" t="n">
-        <v>6799090</v>
+        <v>6798688</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4586,7 +4590,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4596,12 +4600,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Äldre stubbe</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4610,6 +4609,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -20667,50 +20667,45 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>133570748</v>
+        <v>133570831</v>
       </c>
       <c r="B194" t="n">
-        <v>57145</v>
+        <v>79952</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
-      <c r="M194" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P194" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>427447</v>
+        <v>426892</v>
       </c>
       <c r="R194" t="n">
-        <v>6798596</v>
+        <v>6798794</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20742,7 +20737,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -20752,7 +20747,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -20779,7 +20774,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>133570831</v>
+        <v>133570852</v>
       </c>
       <c r="B195" t="n">
         <v>79952</v>
@@ -20814,10 +20809,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>426892</v>
+        <v>426927</v>
       </c>
       <c r="R195" t="n">
-        <v>6798794</v>
+        <v>6798629</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20849,7 +20844,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -20859,7 +20854,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -20886,10 +20881,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>133570852</v>
+        <v>133570841</v>
       </c>
       <c r="B196" t="n">
-        <v>79952</v>
+        <v>79091</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20897,21 +20892,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -20921,10 +20916,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>426927</v>
+        <v>426902</v>
       </c>
       <c r="R196" t="n">
-        <v>6798629</v>
+        <v>6798724</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20956,7 +20951,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -20966,7 +20961,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -20993,53 +20988,48 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>133570752</v>
+        <v>133570342</v>
       </c>
       <c r="B197" t="n">
-        <v>57955</v>
+        <v>93206</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
-      <c r="M197" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P197" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>427462</v>
+        <v>427381</v>
       </c>
       <c r="R197" t="n">
-        <v>6798577</v>
+        <v>6798673</v>
       </c>
       <c r="S197" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -21068,7 +21058,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -21078,7 +21068,12 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC197" t="inlineStr">
+        <is>
+          <t>4 fruktkroppar</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -21093,60 +21088,65 @@
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>133570342</v>
+        <v>133570752</v>
       </c>
       <c r="B198" t="n">
-        <v>93206</v>
+        <v>57955</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P198" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>427381</v>
+        <v>427462</v>
       </c>
       <c r="R198" t="n">
-        <v>6798673</v>
+        <v>6798577</v>
       </c>
       <c r="S198" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -21175,7 +21175,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -21185,12 +21185,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC198" t="inlineStr">
-        <is>
-          <t>4 fruktkroppar</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21205,57 +21200,62 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>133570841</v>
+        <v>133570748</v>
       </c>
       <c r="B199" t="n">
-        <v>79091</v>
+        <v>57145</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P199" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>426902</v>
+        <v>427447</v>
       </c>
       <c r="R199" t="n">
-        <v>6798724</v>
+        <v>6798596</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21287,7 +21287,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -21297,7 +21297,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -21324,32 +21324,32 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>133570313</v>
+        <v>133570781</v>
       </c>
       <c r="B200" t="n">
-        <v>93206</v>
+        <v>79090</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -21359,13 +21359,13 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>426901</v>
+        <v>427226</v>
       </c>
       <c r="R200" t="n">
-        <v>6798678</v>
+        <v>6798493</v>
       </c>
       <c r="S200" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T200" t="inlineStr">
         <is>
@@ -21394,7 +21394,7 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -21404,12 +21404,7 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>09:06</t>
-        </is>
-      </c>
-      <c r="AC200" t="inlineStr">
-        <is>
-          <t>En fruktkropp</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -21424,19 +21419,19 @@
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>133570747</v>
+        <v>133570313</v>
       </c>
       <c r="B201" t="n">
         <v>93206</v>
@@ -21464,24 +21459,20 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I201" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>427439</v>
+        <v>426901</v>
       </c>
       <c r="R201" t="n">
-        <v>6798568</v>
+        <v>6798678</v>
       </c>
       <c r="S201" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -21510,7 +21501,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -21520,7 +21511,12 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>09:06</t>
+        </is>
+      </c>
+      <c r="AC201" t="inlineStr">
+        <is>
+          <t>En fruktkropp</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -21535,60 +21531,64 @@
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>133570363</v>
+        <v>133570747</v>
       </c>
       <c r="B202" t="n">
-        <v>57955</v>
+        <v>93206</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P202" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>427271</v>
+        <v>427439</v>
       </c>
       <c r="R202" t="n">
-        <v>6798327</v>
+        <v>6798568</v>
       </c>
       <c r="S202" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -21617,7 +21617,7 @@
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -21627,12 +21627,7 @@
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>16:31</t>
-        </is>
-      </c>
-      <c r="AC202" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -21647,19 +21642,19 @@
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>133570311</v>
+        <v>133570363</v>
       </c>
       <c r="B203" t="n">
         <v>57955</v>
@@ -21694,10 +21689,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>426863</v>
+        <v>427271</v>
       </c>
       <c r="R203" t="n">
-        <v>6798614</v>
+        <v>6798327</v>
       </c>
       <c r="S203" t="n">
         <v>5</v>
@@ -21729,7 +21724,7 @@
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
@@ -21739,12 +21734,12 @@
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AC203" t="inlineStr">
         <is>
-          <t>Färska spår</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -21771,53 +21766,48 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>133570787</v>
+        <v>133570311</v>
       </c>
       <c r="B204" t="n">
-        <v>57145</v>
+        <v>57955</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
-      <c r="M204" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P204" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>427144</v>
+        <v>426863</v>
       </c>
       <c r="R204" t="n">
-        <v>6798517</v>
+        <v>6798614</v>
       </c>
       <c r="S204" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T204" t="inlineStr">
         <is>
@@ -21846,7 +21836,7 @@
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
@@ -21856,7 +21846,12 @@
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="AC204" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -21871,57 +21866,62 @@
       <c r="AT204" t="inlineStr"/>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>133570781</v>
+        <v>133570787</v>
       </c>
       <c r="B205" t="n">
-        <v>79090</v>
+        <v>57145</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P205" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>427226</v>
+        <v>427144</v>
       </c>
       <c r="R205" t="n">
-        <v>6798493</v>
+        <v>6798517</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -21953,7 +21953,7 @@
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
@@ -21963,7 +21963,7 @@
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -22319,53 +22319,50 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>133570721</v>
+        <v>133570746</v>
       </c>
       <c r="B209" t="n">
-        <v>57958</v>
+        <v>57145</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
-      <c r="K209" t="inlineStr"/>
-      <c r="L209" t="inlineStr"/>
       <c r="M209" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N209" t="inlineStr"/>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P209" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>427577</v>
+        <v>427449</v>
       </c>
       <c r="R209" t="n">
-        <v>6798359</v>
+        <v>6798551</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -22397,7 +22394,7 @@
       </c>
       <c r="Z209" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
@@ -22407,7 +22404,7 @@
       </c>
       <c r="AB209" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -22434,7 +22431,7 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>133570746</v>
+        <v>133570334</v>
       </c>
       <c r="B210" t="n">
         <v>57145</v>
@@ -22463,21 +22460,16 @@
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
-      <c r="M210" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P210" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>427449</v>
+        <v>427306</v>
       </c>
       <c r="R210" t="n">
-        <v>6798551</v>
+        <v>6798482</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -22509,7 +22501,7 @@
       </c>
       <c r="Z210" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
@@ -22519,7 +22511,12 @@
       </c>
       <c r="AB210" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AC210" t="inlineStr">
+        <is>
+          <t>Färsk spillning, höna</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -22534,57 +22531,65 @@
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>133570334</v>
+        <v>133570721</v>
       </c>
       <c r="B211" t="n">
-        <v>57145</v>
+        <v>57958</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
+      <c r="K211" t="inlineStr"/>
+      <c r="L211" t="inlineStr"/>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>427306</v>
+        <v>427577</v>
       </c>
       <c r="R211" t="n">
-        <v>6798482</v>
+        <v>6798359</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -22616,7 +22621,7 @@
       </c>
       <c r="Z211" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
@@ -22626,12 +22631,7 @@
       </c>
       <c r="AB211" t="inlineStr">
         <is>
-          <t>12:57</t>
-        </is>
-      </c>
-      <c r="AC211" t="inlineStr">
-        <is>
-          <t>Färsk spillning, höna</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -22646,12 +22646,12 @@
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
@@ -22877,45 +22877,53 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>133570867</v>
+        <v>133570783</v>
       </c>
       <c r="B214" t="n">
-        <v>79952</v>
+        <v>57145</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
+      <c r="K214" t="inlineStr"/>
+      <c r="L214" t="inlineStr"/>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>426877</v>
+        <v>427211</v>
       </c>
       <c r="R214" t="n">
-        <v>6798609</v>
+        <v>6798464</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -22947,7 +22955,7 @@
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
@@ -22957,7 +22965,7 @@
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -22984,10 +22992,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>133570729</v>
+        <v>133570867</v>
       </c>
       <c r="B215" t="n">
-        <v>79333</v>
+        <v>79952</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -22995,21 +23003,21 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -23019,10 +23027,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>427641</v>
+        <v>426877</v>
       </c>
       <c r="R215" t="n">
-        <v>6798373</v>
+        <v>6798609</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -23054,7 +23062,7 @@
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
@@ -23064,7 +23072,7 @@
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -23091,10 +23099,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>133570783</v>
+        <v>133570782</v>
       </c>
       <c r="B216" t="n">
-        <v>57145</v>
+        <v>93206</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -23102,42 +23110,38 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I216" t="inlineStr"/>
-      <c r="K216" t="inlineStr"/>
-      <c r="L216" t="inlineStr"/>
-      <c r="M216" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N216" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P216" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>427211</v>
+        <v>427236</v>
       </c>
       <c r="R216" t="n">
-        <v>6798464</v>
+        <v>6798479</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -23169,7 +23173,7 @@
       </c>
       <c r="Z216" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
@@ -23179,7 +23183,7 @@
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -23206,49 +23210,45 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>133570782</v>
+        <v>133570729</v>
       </c>
       <c r="B217" t="n">
-        <v>93206</v>
+        <v>79333</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I217" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>427236</v>
+        <v>427641</v>
       </c>
       <c r="R217" t="n">
-        <v>6798479</v>
+        <v>6798373</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -23280,7 +23280,7 @@
       </c>
       <c r="Z217" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
@@ -23290,7 +23290,7 @@
       </c>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -23317,48 +23317,52 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>133570361</v>
+        <v>133570753</v>
       </c>
       <c r="B218" t="n">
-        <v>79333</v>
+        <v>93206</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I218" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P218" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>427570</v>
+        <v>427505</v>
       </c>
       <c r="R218" t="n">
-        <v>6798357</v>
+        <v>6798604</v>
       </c>
       <c r="S218" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T218" t="inlineStr">
         <is>
@@ -23387,7 +23391,7 @@
       </c>
       <c r="Z218" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
@@ -23397,7 +23401,7 @@
       </c>
       <c r="AB218" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -23412,22 +23416,22 @@
       <c r="AT218" t="inlineStr"/>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>133570786</v>
+        <v>133570361</v>
       </c>
       <c r="B219" t="n">
-        <v>57955</v>
+        <v>79333</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -23435,42 +23439,37 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
-      <c r="M219" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P219" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>427254</v>
+        <v>427570</v>
       </c>
       <c r="R219" t="n">
-        <v>6798375</v>
+        <v>6798357</v>
       </c>
       <c r="S219" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T219" t="inlineStr">
         <is>
@@ -23499,7 +23498,7 @@
       </c>
       <c r="Z219" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
@@ -23509,7 +23508,7 @@
       </c>
       <c r="AB219" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -23524,19 +23523,19 @@
       <c r="AT219" t="inlineStr"/>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>133570753</v>
+        <v>133570759</v>
       </c>
       <c r="B220" t="n">
         <v>93206</v>
@@ -23564,21 +23563,17 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I220" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>427505</v>
+        <v>427425</v>
       </c>
       <c r="R220" t="n">
-        <v>6798604</v>
+        <v>6798648</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -23610,7 +23605,7 @@
       </c>
       <c r="Z220" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
@@ -23620,7 +23615,7 @@
       </c>
       <c r="AB220" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -23647,45 +23642,50 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>133570759</v>
+        <v>133570786</v>
       </c>
       <c r="B221" t="n">
-        <v>93206</v>
+        <v>57955</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P221" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>427425</v>
+        <v>427254</v>
       </c>
       <c r="R221" t="n">
-        <v>6798648</v>
+        <v>6798375</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -23717,7 +23717,7 @@
       </c>
       <c r="Z221" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
@@ -23727,7 +23727,7 @@
       </c>
       <c r="AB221" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -23861,48 +23861,57 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>133570357</v>
+        <v>133570858</v>
       </c>
       <c r="B223" t="n">
-        <v>79333</v>
+        <v>8455</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
+      <c r="J223" t="inlineStr"/>
+      <c r="K223" t="inlineStr"/>
+      <c r="L223" t="inlineStr"/>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>427541</v>
+        <v>426896</v>
       </c>
       <c r="R223" t="n">
-        <v>6798424</v>
+        <v>6798616</v>
       </c>
       <c r="S223" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T223" t="inlineStr">
         <is>
@@ -23931,7 +23940,7 @@
       </c>
       <c r="Z223" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
@@ -23941,7 +23950,7 @@
       </c>
       <c r="AB223" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -23950,50 +23959,51 @@
       <c r="AE223" t="b">
         <v>0</v>
       </c>
+      <c r="AF223" t="inlineStr"/>
       <c r="AG223" t="b">
         <v>0</v>
       </c>
       <c r="AT223" t="inlineStr"/>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>133570740</v>
+        <v>133570333</v>
       </c>
       <c r="B224" t="n">
-        <v>79333</v>
+        <v>57145</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -24003,13 +24013,13 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>427511</v>
+        <v>427308</v>
       </c>
       <c r="R224" t="n">
-        <v>6798460</v>
+        <v>6798484</v>
       </c>
       <c r="S224" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="T224" t="inlineStr">
         <is>
@@ -24038,7 +24048,7 @@
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
@@ -24048,7 +24058,12 @@
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AC224" t="inlineStr">
+        <is>
+          <t>Färsk spillning, tupp</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -24063,12 +24078,12 @@
       <c r="AT224" t="inlineStr"/>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
@@ -24401,10 +24416,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>133570720</v>
+        <v>133570357</v>
       </c>
       <c r="B228" t="n">
-        <v>57955</v>
+        <v>79333</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -24412,42 +24427,37 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
-      <c r="M228" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P228" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>427401</v>
+        <v>427541</v>
       </c>
       <c r="R228" t="n">
-        <v>6798415</v>
+        <v>6798424</v>
       </c>
       <c r="S228" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T228" t="inlineStr">
         <is>
@@ -24476,7 +24486,7 @@
       </c>
       <c r="Z228" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
@@ -24486,7 +24496,7 @@
       </c>
       <c r="AB228" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -24501,65 +24511,57 @@
       <c r="AT228" t="inlineStr"/>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>133570756</v>
+        <v>133570740</v>
       </c>
       <c r="B229" t="n">
-        <v>57950</v>
+        <v>79333</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>100110</v>
+        <v>6425</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
-      <c r="K229" t="inlineStr"/>
-      <c r="L229" t="inlineStr"/>
-      <c r="M229" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N229" t="inlineStr"/>
       <c r="P229" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>427481</v>
+        <v>427511</v>
       </c>
       <c r="R229" t="n">
-        <v>6798627</v>
+        <v>6798460</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -24591,7 +24593,7 @@
       </c>
       <c r="Z229" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
@@ -24601,12 +24603,7 @@
       </c>
       <c r="AB229" t="inlineStr">
         <is>
-          <t>14:06</t>
-        </is>
-      </c>
-      <c r="AC229" t="inlineStr">
-        <is>
-          <t>Sågs flyga från trädstam till trädstam och gav även ifrån sig ett läte.</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -24626,55 +24623,60 @@
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>133570333</v>
+        <v>133570720</v>
       </c>
       <c r="B230" t="n">
-        <v>57145</v>
+        <v>57955</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P230" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>427308</v>
+        <v>427401</v>
       </c>
       <c r="R230" t="n">
-        <v>6798484</v>
+        <v>6798415</v>
       </c>
       <c r="S230" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="T230" t="inlineStr">
         <is>
@@ -24703,7 +24705,7 @@
       </c>
       <c r="Z230" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
@@ -24713,12 +24715,7 @@
       </c>
       <c r="AB230" t="inlineStr">
         <is>
-          <t>12:56</t>
-        </is>
-      </c>
-      <c r="AC230" t="inlineStr">
-        <is>
-          <t>Färsk spillning, tupp</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -24733,22 +24730,22 @@
       <c r="AT230" t="inlineStr"/>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>133570858</v>
+        <v>133570756</v>
       </c>
       <c r="B231" t="n">
-        <v>8455</v>
+        <v>57950</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -24756,30 +24753,29 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>106545</v>
+        <v>100110</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
-      <c r="J231" t="inlineStr"/>
       <c r="K231" t="inlineStr"/>
       <c r="L231" t="inlineStr"/>
       <c r="M231" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N231" t="inlineStr"/>
@@ -24789,10 +24785,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>426896</v>
+        <v>427481</v>
       </c>
       <c r="R231" t="n">
-        <v>6798616</v>
+        <v>6798627</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -24824,7 +24820,7 @@
       </c>
       <c r="Z231" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
@@ -24834,7 +24830,12 @@
       </c>
       <c r="AB231" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AC231" t="inlineStr">
+        <is>
+          <t>Sågs flyga från trädstam till trädstam och gav även ifrån sig ett läte.</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -24843,7 +24844,6 @@
       <c r="AE231" t="b">
         <v>0</v>
       </c>
-      <c r="AF231" t="inlineStr"/>
       <c r="AG231" t="b">
         <v>0</v>
       </c>
@@ -24855,7 +24855,7 @@
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Eva Löfqvist, Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
@@ -25187,32 +25187,32 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>133570840</v>
+        <v>133570339</v>
       </c>
       <c r="B235" t="n">
-        <v>106243</v>
+        <v>57955</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>221725</v>
+        <v>100049</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
@@ -25222,13 +25222,13 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>426891</v>
+        <v>427177</v>
       </c>
       <c r="R235" t="n">
-        <v>6798759</v>
+        <v>6798702</v>
       </c>
       <c r="S235" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T235" t="inlineStr">
         <is>
@@ -25257,7 +25257,7 @@
       </c>
       <c r="Z235" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA235" t="inlineStr">
@@ -25267,7 +25267,12 @@
       </c>
       <c r="AB235" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AC235" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -25282,44 +25287,44 @@
       <c r="AT235" t="inlineStr"/>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>133570339</v>
+        <v>133570840</v>
       </c>
       <c r="B236" t="n">
-        <v>57955</v>
+        <v>106243</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>100049</v>
+        <v>221725</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
@@ -25329,13 +25334,13 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>427177</v>
+        <v>426891</v>
       </c>
       <c r="R236" t="n">
-        <v>6798702</v>
+        <v>6798759</v>
       </c>
       <c r="S236" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T236" t="inlineStr">
         <is>
@@ -25364,7 +25369,7 @@
       </c>
       <c r="Z236" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
@@ -25374,12 +25379,7 @@
       </c>
       <c r="AB236" t="inlineStr">
         <is>
-          <t>13:31</t>
-        </is>
-      </c>
-      <c r="AC236" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -25394,12 +25394,12 @@
       <c r="AT236" t="inlineStr"/>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
@@ -25966,50 +25966,45 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>133570776</v>
+        <v>133570851</v>
       </c>
       <c r="B242" t="n">
-        <v>57145</v>
+        <v>79952</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
-      <c r="M242" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P242" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>427301</v>
+        <v>426929</v>
       </c>
       <c r="R242" t="n">
-        <v>6798484</v>
+        <v>6798628</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -26041,7 +26036,7 @@
       </c>
       <c r="Z242" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
@@ -26051,7 +26046,7 @@
       </c>
       <c r="AB242" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -26078,10 +26073,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>133570851</v>
+        <v>133570815</v>
       </c>
       <c r="B243" t="n">
-        <v>79952</v>
+        <v>79090</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -26089,21 +26084,21 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -26113,10 +26108,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>426929</v>
+        <v>426859</v>
       </c>
       <c r="R243" t="n">
-        <v>6798628</v>
+        <v>6798952</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -26148,7 +26143,7 @@
       </c>
       <c r="Z243" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr">
@@ -26158,7 +26153,7 @@
       </c>
       <c r="AB243" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -26185,10 +26180,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>133570815</v>
+        <v>133570766</v>
       </c>
       <c r="B244" t="n">
-        <v>79090</v>
+        <v>79333</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -26196,21 +26191,21 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
@@ -26220,10 +26215,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>426859</v>
+        <v>427267</v>
       </c>
       <c r="R244" t="n">
-        <v>6798952</v>
+        <v>6798730</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -26255,7 +26250,7 @@
       </c>
       <c r="Z244" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
@@ -26265,7 +26260,7 @@
       </c>
       <c r="AB244" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -26292,45 +26287,50 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>133570766</v>
+        <v>133570776</v>
       </c>
       <c r="B245" t="n">
-        <v>79333</v>
+        <v>57145</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P245" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>427267</v>
+        <v>427301</v>
       </c>
       <c r="R245" t="n">
-        <v>6798730</v>
+        <v>6798484</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -26362,7 +26362,7 @@
       </c>
       <c r="Z245" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
@@ -26372,7 +26372,7 @@
       </c>
       <c r="AB245" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -26514,10 +26514,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>133570816</v>
+        <v>133570732</v>
       </c>
       <c r="B247" t="n">
-        <v>79952</v>
+        <v>57958</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -26525,34 +26525,42 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
+      <c r="K247" t="inlineStr"/>
+      <c r="L247" t="inlineStr"/>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N247" t="inlineStr"/>
       <c r="P247" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>426859</v>
+        <v>427617</v>
       </c>
       <c r="R247" t="n">
-        <v>6798955</v>
+        <v>6798425</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -26584,7 +26592,7 @@
       </c>
       <c r="Z247" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA247" t="inlineStr">
@@ -26594,7 +26602,12 @@
       </c>
       <c r="AB247" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AC247" t="inlineStr">
+        <is>
+          <t>färska ringhack med kåda.</t>
         </is>
       </c>
       <c r="AD247" t="b">
@@ -26621,32 +26634,32 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>133570827</v>
+        <v>133570358</v>
       </c>
       <c r="B248" t="n">
-        <v>79952</v>
+        <v>57145</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
@@ -26656,13 +26669,13 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>426914</v>
+        <v>427596</v>
       </c>
       <c r="R248" t="n">
-        <v>6798802</v>
+        <v>6798420</v>
       </c>
       <c r="S248" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T248" t="inlineStr">
         <is>
@@ -26691,7 +26704,7 @@
       </c>
       <c r="Z248" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
@@ -26701,7 +26714,12 @@
       </c>
       <c r="AB248" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AC248" t="inlineStr">
+        <is>
+          <t>Färsk spillning tupp</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -26716,22 +26734,22 @@
       <c r="AT248" t="inlineStr"/>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>133570732</v>
+        <v>133570861</v>
       </c>
       <c r="B249" t="n">
-        <v>57958</v>
+        <v>79091</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -26739,42 +26757,34 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
-      <c r="K249" t="inlineStr"/>
-      <c r="L249" t="inlineStr"/>
-      <c r="M249" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>427617</v>
+        <v>426896</v>
       </c>
       <c r="R249" t="n">
-        <v>6798425</v>
+        <v>6798604</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -26806,7 +26816,7 @@
       </c>
       <c r="Z249" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA249" t="inlineStr">
@@ -26816,12 +26826,7 @@
       </c>
       <c r="AB249" t="inlineStr">
         <is>
-          <t>15:10</t>
-        </is>
-      </c>
-      <c r="AC249" t="inlineStr">
-        <is>
-          <t>färska ringhack med kåda.</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -26848,32 +26853,32 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>133570358</v>
+        <v>133570816</v>
       </c>
       <c r="B250" t="n">
-        <v>57145</v>
+        <v>79952</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
@@ -26883,13 +26888,13 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>427596</v>
+        <v>426859</v>
       </c>
       <c r="R250" t="n">
-        <v>6798420</v>
+        <v>6798955</v>
       </c>
       <c r="S250" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T250" t="inlineStr">
         <is>
@@ -26918,7 +26923,7 @@
       </c>
       <c r="Z250" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
@@ -26928,12 +26933,7 @@
       </c>
       <c r="AB250" t="inlineStr">
         <is>
-          <t>14:54</t>
-        </is>
-      </c>
-      <c r="AC250" t="inlineStr">
-        <is>
-          <t>Färsk spillning tupp</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -26948,22 +26948,22 @@
       <c r="AT250" t="inlineStr"/>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>133570861</v>
+        <v>133570827</v>
       </c>
       <c r="B251" t="n">
-        <v>79091</v>
+        <v>79952</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -26971,21 +26971,21 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
@@ -26995,10 +26995,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>426896</v>
+        <v>426914</v>
       </c>
       <c r="R251" t="n">
-        <v>6798604</v>
+        <v>6798802</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -27030,7 +27030,7 @@
       </c>
       <c r="Z251" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA251" t="inlineStr">
@@ -27040,7 +27040,7 @@
       </c>
       <c r="AB251" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -27500,10 +27500,10 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>133570341</v>
+        <v>133570820</v>
       </c>
       <c r="B256" t="n">
-        <v>79333</v>
+        <v>79952</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -27511,21 +27511,21 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
@@ -27535,13 +27535,13 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>427374</v>
+        <v>426853</v>
       </c>
       <c r="R256" t="n">
-        <v>6798672</v>
+        <v>6798894</v>
       </c>
       <c r="S256" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T256" t="inlineStr">
         <is>
@@ -27570,7 +27570,7 @@
       </c>
       <c r="Z256" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA256" t="inlineStr">
@@ -27580,7 +27580,7 @@
       </c>
       <c r="AB256" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD256" t="b">
@@ -27595,19 +27595,19 @@
       <c r="AT256" t="inlineStr"/>
       <c r="AW256" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>133570733</v>
+        <v>133570341</v>
       </c>
       <c r="B257" t="n">
         <v>79333</v>
@@ -27642,13 +27642,13 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>427626</v>
+        <v>427374</v>
       </c>
       <c r="R257" t="n">
-        <v>6798413</v>
+        <v>6798672</v>
       </c>
       <c r="S257" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T257" t="inlineStr">
         <is>
@@ -27677,7 +27677,7 @@
       </c>
       <c r="Z257" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA257" t="inlineStr">
@@ -27687,7 +27687,7 @@
       </c>
       <c r="AB257" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD257" t="b">
@@ -27702,19 +27702,19 @@
       <c r="AT257" t="inlineStr"/>
       <c r="AW257" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>133570345</v>
+        <v>133570733</v>
       </c>
       <c r="B258" t="n">
         <v>79333</v>
@@ -27743,22 +27743,19 @@
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
-      <c r="J258" t="inlineStr"/>
-      <c r="K258" t="inlineStr"/>
-      <c r="N258" t="inlineStr"/>
       <c r="P258" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>427484</v>
+        <v>427626</v>
       </c>
       <c r="R258" t="n">
-        <v>6798636</v>
+        <v>6798413</v>
       </c>
       <c r="S258" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T258" t="inlineStr">
         <is>
@@ -27787,7 +27784,7 @@
       </c>
       <c r="Z258" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA258" t="inlineStr">
@@ -27797,7 +27794,7 @@
       </c>
       <c r="AB258" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD258" t="b">
@@ -27806,29 +27803,28 @@
       <c r="AE258" t="b">
         <v>0</v>
       </c>
-      <c r="AF258" t="inlineStr"/>
       <c r="AG258" t="b">
         <v>0</v>
       </c>
       <c r="AT258" t="inlineStr"/>
       <c r="AW258" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>133570820</v>
+        <v>133570345</v>
       </c>
       <c r="B259" t="n">
-        <v>79952</v>
+        <v>79333</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -27836,37 +27832,40 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
+      <c r="J259" t="inlineStr"/>
+      <c r="K259" t="inlineStr"/>
+      <c r="N259" t="inlineStr"/>
       <c r="P259" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>426853</v>
+        <v>427484</v>
       </c>
       <c r="R259" t="n">
-        <v>6798894</v>
+        <v>6798636</v>
       </c>
       <c r="S259" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T259" t="inlineStr">
         <is>
@@ -27895,7 +27894,7 @@
       </c>
       <c r="Z259" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA259" t="inlineStr">
@@ -27905,7 +27904,7 @@
       </c>
       <c r="AB259" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD259" t="b">
@@ -27914,18 +27913,19 @@
       <c r="AE259" t="b">
         <v>0</v>
       </c>
+      <c r="AF259" t="inlineStr"/>
       <c r="AG259" t="b">
         <v>0</v>
       </c>
       <c r="AT259" t="inlineStr"/>
       <c r="AW259" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
@@ -28159,10 +28159,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>133570739</v>
+        <v>133570845</v>
       </c>
       <c r="B262" t="n">
-        <v>79333</v>
+        <v>79952</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -28170,21 +28170,21 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
@@ -28194,10 +28194,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>427503</v>
+        <v>426923</v>
       </c>
       <c r="R262" t="n">
-        <v>6798447</v>
+        <v>6798703</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -28229,7 +28229,7 @@
       </c>
       <c r="Z262" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA262" t="inlineStr">
@@ -28239,7 +28239,7 @@
       </c>
       <c r="AB262" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD262" t="b">
@@ -28266,10 +28266,10 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>133570845</v>
+        <v>133570849</v>
       </c>
       <c r="B263" t="n">
-        <v>79952</v>
+        <v>79090</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -28277,21 +28277,21 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
@@ -28301,10 +28301,10 @@
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>426923</v>
+        <v>426932</v>
       </c>
       <c r="R263" t="n">
-        <v>6798703</v>
+        <v>6798677</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -28336,7 +28336,7 @@
       </c>
       <c r="Z263" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA263" t="inlineStr">
@@ -28346,7 +28346,7 @@
       </c>
       <c r="AB263" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD263" t="b">
@@ -28373,7 +28373,7 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>133570849</v>
+        <v>133570857</v>
       </c>
       <c r="B264" t="n">
         <v>79090</v>
@@ -28408,10 +28408,10 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>426932</v>
+        <v>426896</v>
       </c>
       <c r="R264" t="n">
-        <v>6798677</v>
+        <v>6798620</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -28443,7 +28443,7 @@
       </c>
       <c r="Z264" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA264" t="inlineStr">
@@ -28453,7 +28453,7 @@
       </c>
       <c r="AB264" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD264" t="b">
@@ -28480,7 +28480,7 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>133570346</v>
+        <v>133570739</v>
       </c>
       <c r="B265" t="n">
         <v>79333</v>
@@ -28515,13 +28515,13 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>427507</v>
+        <v>427503</v>
       </c>
       <c r="R265" t="n">
-        <v>6798599</v>
+        <v>6798447</v>
       </c>
       <c r="S265" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T265" t="inlineStr">
         <is>
@@ -28550,7 +28550,7 @@
       </c>
       <c r="Z265" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA265" t="inlineStr">
@@ -28560,7 +28560,7 @@
       </c>
       <c r="AB265" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD265" t="b">
@@ -28575,57 +28575,64 @@
       <c r="AT265" t="inlineStr"/>
       <c r="AW265" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>133570857</v>
+        <v>133570818</v>
       </c>
       <c r="B266" t="n">
-        <v>79090</v>
+        <v>93206</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E266" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I266" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr"/>
+      <c r="K266" t="inlineStr"/>
+      <c r="N266" t="inlineStr"/>
       <c r="P266" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>426896</v>
+        <v>426852</v>
       </c>
       <c r="R266" t="n">
-        <v>6798620</v>
+        <v>6798897</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -28657,7 +28664,7 @@
       </c>
       <c r="Z266" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA266" t="inlineStr">
@@ -28667,7 +28674,7 @@
       </c>
       <c r="AB266" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD266" t="b">
@@ -28676,6 +28683,7 @@
       <c r="AE266" t="b">
         <v>0</v>
       </c>
+      <c r="AF266" t="inlineStr"/>
       <c r="AG266" t="b">
         <v>0</v>
       </c>
@@ -28694,7 +28702,7 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>133570769</v>
+        <v>133570346</v>
       </c>
       <c r="B267" t="n">
         <v>79333</v>
@@ -28729,13 +28737,13 @@
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>427309</v>
+        <v>427507</v>
       </c>
       <c r="R267" t="n">
-        <v>6798726</v>
+        <v>6798599</v>
       </c>
       <c r="S267" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T267" t="inlineStr">
         <is>
@@ -28764,7 +28772,7 @@
       </c>
       <c r="Z267" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA267" t="inlineStr">
@@ -28774,7 +28782,7 @@
       </c>
       <c r="AB267" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD267" t="b">
@@ -28789,62 +28797,57 @@
       <c r="AT267" t="inlineStr"/>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>133570758</v>
+        <v>133570769</v>
       </c>
       <c r="B268" t="n">
-        <v>57145</v>
+        <v>79333</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
-      <c r="M268" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P268" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>427432</v>
+        <v>427309</v>
       </c>
       <c r="R268" t="n">
-        <v>6798638</v>
+        <v>6798726</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -28876,7 +28879,7 @@
       </c>
       <c r="Z268" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA268" t="inlineStr">
@@ -28886,7 +28889,7 @@
       </c>
       <c r="AB268" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD268" t="b">
@@ -28913,55 +28916,48 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>133570818</v>
+        <v>133570336</v>
       </c>
       <c r="B269" t="n">
-        <v>93206</v>
+        <v>57955</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I269" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J269" t="inlineStr"/>
-      <c r="K269" t="inlineStr"/>
-      <c r="N269" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr"/>
       <c r="P269" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>426852</v>
+        <v>427282</v>
       </c>
       <c r="R269" t="n">
-        <v>6798897</v>
+        <v>6798727</v>
       </c>
       <c r="S269" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T269" t="inlineStr">
         <is>
@@ -28990,7 +28986,7 @@
       </c>
       <c r="Z269" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA269" t="inlineStr">
@@ -29000,7 +28996,12 @@
       </c>
       <c r="AB269" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AC269" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD269" t="b">
@@ -29009,67 +29010,71 @@
       <c r="AE269" t="b">
         <v>0</v>
       </c>
-      <c r="AF269" t="inlineStr"/>
       <c r="AG269" t="b">
         <v>0</v>
       </c>
       <c r="AT269" t="inlineStr"/>
       <c r="AW269" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>133570336</v>
+        <v>133570758</v>
       </c>
       <c r="B270" t="n">
-        <v>57955</v>
+        <v>57145</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E270" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P270" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>427282</v>
+        <v>427432</v>
       </c>
       <c r="R270" t="n">
-        <v>6798727</v>
+        <v>6798638</v>
       </c>
       <c r="S270" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T270" t="inlineStr">
         <is>
@@ -29098,7 +29103,7 @@
       </c>
       <c r="Z270" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA270" t="inlineStr">
@@ -29108,12 +29113,7 @@
       </c>
       <c r="AB270" t="inlineStr">
         <is>
-          <t>13:17</t>
-        </is>
-      </c>
-      <c r="AC270" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD270" t="b">
@@ -29128,63 +29128,60 @@
       <c r="AT270" t="inlineStr"/>
       <c r="AW270" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>133570850</v>
+        <v>133570329</v>
       </c>
       <c r="B271" t="n">
-        <v>79952</v>
+        <v>57145</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E271" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
-      <c r="J271" t="inlineStr"/>
-      <c r="K271" t="inlineStr"/>
-      <c r="N271" t="inlineStr"/>
       <c r="P271" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>426946</v>
+        <v>427281</v>
       </c>
       <c r="R271" t="n">
-        <v>6798659</v>
+        <v>6798466</v>
       </c>
       <c r="S271" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T271" t="inlineStr">
         <is>
@@ -29213,7 +29210,7 @@
       </c>
       <c r="Z271" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA271" t="inlineStr">
@@ -29223,7 +29220,12 @@
       </c>
       <c r="AB271" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AC271" t="inlineStr">
+        <is>
+          <t>Färsk spillning höna</t>
         </is>
       </c>
       <c r="AD271" t="b">
@@ -29232,57 +29234,56 @@
       <c r="AE271" t="b">
         <v>0</v>
       </c>
-      <c r="AF271" t="inlineStr"/>
       <c r="AG271" t="b">
         <v>0</v>
       </c>
       <c r="AT271" t="inlineStr"/>
       <c r="AW271" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX271" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>133570817</v>
+        <v>133570742</v>
       </c>
       <c r="B272" t="n">
-        <v>57955</v>
+        <v>57145</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
       <c r="M272" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P272" t="inlineStr">
@@ -29291,10 +29292,10 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>426860</v>
+        <v>427499</v>
       </c>
       <c r="R272" t="n">
-        <v>6798955</v>
+        <v>6798481</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -29326,7 +29327,7 @@
       </c>
       <c r="Z272" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA272" t="inlineStr">
@@ -29336,7 +29337,7 @@
       </c>
       <c r="AB272" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD272" t="b">
@@ -29363,10 +29364,10 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>133570765</v>
+        <v>133570850</v>
       </c>
       <c r="B273" t="n">
-        <v>57955</v>
+        <v>79952</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -29374,39 +29375,37 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
-      <c r="M273" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J273" t="inlineStr"/>
+      <c r="K273" t="inlineStr"/>
+      <c r="N273" t="inlineStr"/>
       <c r="P273" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>427230</v>
+        <v>426946</v>
       </c>
       <c r="R273" t="n">
-        <v>6798732</v>
+        <v>6798659</v>
       </c>
       <c r="S273" t="n">
         <v>10</v>
@@ -29438,7 +29437,7 @@
       </c>
       <c r="Z273" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA273" t="inlineStr">
@@ -29448,7 +29447,7 @@
       </c>
       <c r="AB273" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AD273" t="b">
@@ -29457,6 +29456,7 @@
       <c r="AE273" t="b">
         <v>0</v>
       </c>
+      <c r="AF273" t="inlineStr"/>
       <c r="AG273" t="b">
         <v>0</v>
       </c>
@@ -29475,38 +29475,38 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>133570742</v>
+        <v>133570817</v>
       </c>
       <c r="B274" t="n">
-        <v>57145</v>
+        <v>57955</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
       <c r="M274" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P274" t="inlineStr">
@@ -29515,10 +29515,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>427499</v>
+        <v>426860</v>
       </c>
       <c r="R274" t="n">
-        <v>6798481</v>
+        <v>6798955</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -29550,7 +29550,7 @@
       </c>
       <c r="Z274" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA274" t="inlineStr">
@@ -29560,7 +29560,7 @@
       </c>
       <c r="AB274" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD274" t="b">
@@ -29587,48 +29587,53 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>133570329</v>
+        <v>133570765</v>
       </c>
       <c r="B275" t="n">
-        <v>57145</v>
+        <v>57955</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P275" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>427281</v>
+        <v>427230</v>
       </c>
       <c r="R275" t="n">
-        <v>6798466</v>
+        <v>6798732</v>
       </c>
       <c r="S275" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T275" t="inlineStr">
         <is>
@@ -29657,7 +29662,7 @@
       </c>
       <c r="Z275" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA275" t="inlineStr">
@@ -29667,12 +29672,7 @@
       </c>
       <c r="AB275" t="inlineStr">
         <is>
-          <t>12:47</t>
-        </is>
-      </c>
-      <c r="AC275" t="inlineStr">
-        <is>
-          <t>Färsk spillning höna</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD275" t="b">
@@ -29687,44 +29687,44 @@
       <c r="AT275" t="inlineStr"/>
       <c r="AW275" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX275" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>133570862</v>
+        <v>133570731</v>
       </c>
       <c r="B276" t="n">
-        <v>79952</v>
+        <v>106243</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>6453</v>
+        <v>221725</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
@@ -29734,10 +29734,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>426896</v>
+        <v>427595</v>
       </c>
       <c r="R276" t="n">
-        <v>6798605</v>
+        <v>6798440</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -29769,7 +29769,7 @@
       </c>
       <c r="Z276" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA276" t="inlineStr">
@@ -29779,7 +29779,7 @@
       </c>
       <c r="AB276" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD276" t="b">
@@ -29806,10 +29806,10 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>133570340</v>
+        <v>133570862</v>
       </c>
       <c r="B277" t="n">
-        <v>79090</v>
+        <v>79952</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -29817,21 +29817,21 @@
         </is>
       </c>
       <c r="E277" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I277" t="inlineStr"/>
@@ -29841,13 +29841,13 @@
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>427316</v>
+        <v>426896</v>
       </c>
       <c r="R277" t="n">
-        <v>6798744</v>
+        <v>6798605</v>
       </c>
       <c r="S277" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T277" t="inlineStr">
         <is>
@@ -29876,7 +29876,7 @@
       </c>
       <c r="Z277" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA277" t="inlineStr">
@@ -29886,7 +29886,7 @@
       </c>
       <c r="AB277" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD277" t="b">
@@ -29901,22 +29901,22 @@
       <c r="AT277" t="inlineStr"/>
       <c r="AW277" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX277" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>133570768</v>
+        <v>133570340</v>
       </c>
       <c r="B278" t="n">
-        <v>79333</v>
+        <v>79090</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -29924,21 +29924,21 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
@@ -29948,13 +29948,13 @@
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>427280</v>
+        <v>427316</v>
       </c>
       <c r="R278" t="n">
-        <v>6798731</v>
+        <v>6798744</v>
       </c>
       <c r="S278" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T278" t="inlineStr">
         <is>
@@ -29983,7 +29983,7 @@
       </c>
       <c r="Z278" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA278" t="inlineStr">
@@ -29993,7 +29993,7 @@
       </c>
       <c r="AB278" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD278" t="b">
@@ -30008,65 +30008,60 @@
       <c r="AT278" t="inlineStr"/>
       <c r="AW278" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX278" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>133570760</v>
+        <v>133570344</v>
       </c>
       <c r="B279" t="n">
-        <v>57955</v>
+        <v>93206</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
-      <c r="M279" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P279" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>427373</v>
+        <v>427445</v>
       </c>
       <c r="R279" t="n">
-        <v>6798670</v>
+        <v>6798651</v>
       </c>
       <c r="S279" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T279" t="inlineStr">
         <is>
@@ -30095,7 +30090,7 @@
       </c>
       <c r="Z279" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA279" t="inlineStr">
@@ -30105,7 +30100,7 @@
       </c>
       <c r="AB279" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD279" t="b">
@@ -30120,22 +30115,22 @@
       <c r="AT279" t="inlineStr"/>
       <c r="AW279" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX279" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>133570326</v>
+        <v>133570768</v>
       </c>
       <c r="B280" t="n">
-        <v>57955</v>
+        <v>79333</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -30143,21 +30138,21 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
@@ -30167,13 +30162,13 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>427249</v>
+        <v>427280</v>
       </c>
       <c r="R280" t="n">
-        <v>6798387</v>
+        <v>6798731</v>
       </c>
       <c r="S280" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T280" t="inlineStr">
         <is>
@@ -30202,7 +30197,7 @@
       </c>
       <c r="Z280" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA280" t="inlineStr">
@@ -30212,12 +30207,7 @@
       </c>
       <c r="AB280" t="inlineStr">
         <is>
-          <t>12:36</t>
-        </is>
-      </c>
-      <c r="AC280" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD280" t="b">
@@ -30232,19 +30222,19 @@
       <c r="AT280" t="inlineStr"/>
       <c r="AW280" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX280" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>133570757</v>
+        <v>133570749</v>
       </c>
       <c r="B281" t="n">
         <v>57955</v>
@@ -30284,10 +30274,10 @@
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>427447</v>
+        <v>427437</v>
       </c>
       <c r="R281" t="n">
-        <v>6798639</v>
+        <v>6798580</v>
       </c>
       <c r="S281" t="n">
         <v>10</v>
@@ -30319,7 +30309,7 @@
       </c>
       <c r="Z281" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA281" t="inlineStr">
@@ -30329,7 +30319,7 @@
       </c>
       <c r="AB281" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD281" t="b">
@@ -30356,7 +30346,7 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>133570743</v>
+        <v>133570760</v>
       </c>
       <c r="B282" t="n">
         <v>57955</v>
@@ -30396,10 +30386,10 @@
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>427480</v>
+        <v>427373</v>
       </c>
       <c r="R282" t="n">
-        <v>6798520</v>
+        <v>6798670</v>
       </c>
       <c r="S282" t="n">
         <v>10</v>
@@ -30431,7 +30421,7 @@
       </c>
       <c r="Z282" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA282" t="inlineStr">
@@ -30441,7 +30431,7 @@
       </c>
       <c r="AB282" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD282" t="b">
@@ -30468,7 +30458,7 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>133570727</v>
+        <v>133570326</v>
       </c>
       <c r="B283" t="n">
         <v>57955</v>
@@ -30497,24 +30487,19 @@
         </is>
       </c>
       <c r="I283" t="inlineStr"/>
-      <c r="M283" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P283" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>427647</v>
+        <v>427249</v>
       </c>
       <c r="R283" t="n">
-        <v>6798372</v>
+        <v>6798387</v>
       </c>
       <c r="S283" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T283" t="inlineStr">
         <is>
@@ -30543,7 +30528,7 @@
       </c>
       <c r="Z283" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA283" t="inlineStr">
@@ -30553,7 +30538,12 @@
       </c>
       <c r="AB283" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AC283" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD283" t="b">
@@ -30568,19 +30558,19 @@
       <c r="AT283" t="inlineStr"/>
       <c r="AW283" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX283" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>133570749</v>
+        <v>133570757</v>
       </c>
       <c r="B284" t="n">
         <v>57955</v>
@@ -30620,10 +30610,10 @@
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>427437</v>
+        <v>427447</v>
       </c>
       <c r="R284" t="n">
-        <v>6798580</v>
+        <v>6798639</v>
       </c>
       <c r="S284" t="n">
         <v>10</v>
@@ -30655,7 +30645,7 @@
       </c>
       <c r="Z284" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA284" t="inlineStr">
@@ -30665,7 +30655,7 @@
       </c>
       <c r="AB284" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD284" t="b">
@@ -30692,38 +30682,38 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>133570772</v>
+        <v>133570743</v>
       </c>
       <c r="B285" t="n">
-        <v>57145</v>
+        <v>57955</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I285" t="inlineStr"/>
       <c r="M285" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P285" t="inlineStr">
@@ -30732,10 +30722,10 @@
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>427329</v>
+        <v>427480</v>
       </c>
       <c r="R285" t="n">
-        <v>6798489</v>
+        <v>6798520</v>
       </c>
       <c r="S285" t="n">
         <v>10</v>
@@ -30767,7 +30757,7 @@
       </c>
       <c r="Z285" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA285" t="inlineStr">
@@ -30777,7 +30767,7 @@
       </c>
       <c r="AB285" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD285" t="b">
@@ -30804,48 +30794,53 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>133570344</v>
+        <v>133570727</v>
       </c>
       <c r="B286" t="n">
-        <v>93206</v>
+        <v>57955</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E286" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I286" t="inlineStr"/>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P286" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>427445</v>
+        <v>427647</v>
       </c>
       <c r="R286" t="n">
-        <v>6798651</v>
+        <v>6798372</v>
       </c>
       <c r="S286" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T286" t="inlineStr">
         <is>
@@ -30874,7 +30869,7 @@
       </c>
       <c r="Z286" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA286" t="inlineStr">
@@ -30884,7 +30879,7 @@
       </c>
       <c r="AB286" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD286" t="b">
@@ -30899,22 +30894,22 @@
       <c r="AT286" t="inlineStr"/>
       <c r="AW286" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX286" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>133570731</v>
+        <v>133570772</v>
       </c>
       <c r="B287" t="n">
-        <v>106243</v>
+        <v>57145</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -30922,34 +30917,39 @@
         </is>
       </c>
       <c r="E287" t="n">
-        <v>221725</v>
+        <v>100138</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I287" t="inlineStr"/>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P287" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>427595</v>
+        <v>427329</v>
       </c>
       <c r="R287" t="n">
-        <v>6798440</v>
+        <v>6798489</v>
       </c>
       <c r="S287" t="n">
         <v>10</v>
@@ -30981,7 +30981,7 @@
       </c>
       <c r="Z287" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA287" t="inlineStr">
@@ -30991,7 +30991,7 @@
       </c>
       <c r="AB287" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD287" t="b">
@@ -31018,10 +31018,10 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>133570762</v>
+        <v>133570362</v>
       </c>
       <c r="B288" t="n">
-        <v>56522</v>
+        <v>79333</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -31029,42 +31029,37 @@
         </is>
       </c>
       <c r="E288" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I288" t="inlineStr"/>
-      <c r="M288" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P288" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q288" t="n">
-        <v>427205</v>
+        <v>427452</v>
       </c>
       <c r="R288" t="n">
-        <v>6798756</v>
+        <v>6798410</v>
       </c>
       <c r="S288" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T288" t="inlineStr">
         <is>
@@ -31093,7 +31088,7 @@
       </c>
       <c r="Z288" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA288" t="inlineStr">
@@ -31103,7 +31098,7 @@
       </c>
       <c r="AB288" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD288" t="b">
@@ -31118,44 +31113,44 @@
       <c r="AT288" t="inlineStr"/>
       <c r="AW288" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX288" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>133570362</v>
+        <v>133570330</v>
       </c>
       <c r="B289" t="n">
-        <v>79333</v>
+        <v>57145</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E289" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I289" t="inlineStr"/>
@@ -31165,10 +31160,10 @@
         </is>
       </c>
       <c r="Q289" t="n">
-        <v>427452</v>
+        <v>427301</v>
       </c>
       <c r="R289" t="n">
-        <v>6798410</v>
+        <v>6798481</v>
       </c>
       <c r="S289" t="n">
         <v>5</v>
@@ -31200,7 +31195,7 @@
       </c>
       <c r="Z289" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA289" t="inlineStr">
@@ -31210,7 +31205,12 @@
       </c>
       <c r="AB289" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC289" t="inlineStr">
+        <is>
+          <t>Färsk spillning, tupp</t>
         </is>
       </c>
       <c r="AD289" t="b">
@@ -31237,27 +31237,27 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>133570330</v>
+        <v>133570762</v>
       </c>
       <c r="B290" t="n">
-        <v>57145</v>
+        <v>56522</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E290" t="n">
-        <v>100138</v>
+        <v>206004</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -31266,19 +31266,24 @@
         </is>
       </c>
       <c r="I290" t="inlineStr"/>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P290" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q290" t="n">
-        <v>427301</v>
+        <v>427205</v>
       </c>
       <c r="R290" t="n">
-        <v>6798481</v>
+        <v>6798756</v>
       </c>
       <c r="S290" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T290" t="inlineStr">
         <is>
@@ -31307,7 +31312,7 @@
       </c>
       <c r="Z290" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA290" t="inlineStr">
@@ -31317,12 +31322,7 @@
       </c>
       <c r="AB290" t="inlineStr">
         <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC290" t="inlineStr">
-        <is>
-          <t>Färsk spillning, tupp</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD290" t="b">
@@ -31337,22 +31337,22 @@
       <c r="AT290" t="inlineStr"/>
       <c r="AW290" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX290" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>133570738</v>
+        <v>133570825</v>
       </c>
       <c r="B291" t="n">
-        <v>79333</v>
+        <v>79952</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -31360,21 +31360,21 @@
         </is>
       </c>
       <c r="E291" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I291" t="inlineStr"/>
@@ -31384,10 +31384,10 @@
         </is>
       </c>
       <c r="Q291" t="n">
-        <v>427504</v>
+        <v>426913</v>
       </c>
       <c r="R291" t="n">
-        <v>6798429</v>
+        <v>6798823</v>
       </c>
       <c r="S291" t="n">
         <v>10</v>
@@ -31419,7 +31419,7 @@
       </c>
       <c r="Z291" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA291" t="inlineStr">
@@ -31429,7 +31429,7 @@
       </c>
       <c r="AB291" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD291" t="b">
@@ -31456,10 +31456,10 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>133570353</v>
+        <v>133570325</v>
       </c>
       <c r="B292" t="n">
-        <v>79333</v>
+        <v>79090</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -31467,34 +31467,37 @@
         </is>
       </c>
       <c r="E292" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I292" t="inlineStr"/>
+      <c r="J292" t="inlineStr"/>
+      <c r="K292" t="inlineStr"/>
+      <c r="N292" t="inlineStr"/>
       <c r="P292" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q292" t="n">
-        <v>427523</v>
+        <v>427249</v>
       </c>
       <c r="R292" t="n">
-        <v>6798453</v>
+        <v>6798389</v>
       </c>
       <c r="S292" t="n">
         <v>5</v>
@@ -31526,7 +31529,7 @@
       </c>
       <c r="Z292" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA292" t="inlineStr">
@@ -31536,7 +31539,12 @@
       </c>
       <c r="AB292" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AC292" t="inlineStr">
+        <is>
+          <t>Brandstubbe</t>
         </is>
       </c>
       <c r="AD292" t="b">
@@ -31545,6 +31553,7 @@
       <c r="AE292" t="b">
         <v>0</v>
       </c>
+      <c r="AF292" t="inlineStr"/>
       <c r="AG292" t="b">
         <v>0</v>
       </c>
@@ -31563,10 +31572,10 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>133570825</v>
+        <v>133570842</v>
       </c>
       <c r="B293" t="n">
-        <v>79952</v>
+        <v>79090</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -31574,34 +31583,37 @@
         </is>
       </c>
       <c r="E293" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I293" t="inlineStr"/>
+      <c r="J293" t="inlineStr"/>
+      <c r="K293" t="inlineStr"/>
+      <c r="N293" t="inlineStr"/>
       <c r="P293" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q293" t="n">
-        <v>426913</v>
+        <v>426905</v>
       </c>
       <c r="R293" t="n">
-        <v>6798823</v>
+        <v>6798726</v>
       </c>
       <c r="S293" t="n">
         <v>10</v>
@@ -31633,7 +31645,7 @@
       </c>
       <c r="Z293" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA293" t="inlineStr">
@@ -31643,7 +31655,7 @@
       </c>
       <c r="AB293" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD293" t="b">
@@ -31652,6 +31664,7 @@
       <c r="AE293" t="b">
         <v>0</v>
       </c>
+      <c r="AF293" t="inlineStr"/>
       <c r="AG293" t="b">
         <v>0</v>
       </c>
@@ -31670,10 +31683,10 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>133570325</v>
+        <v>133570738</v>
       </c>
       <c r="B294" t="n">
-        <v>79090</v>
+        <v>79333</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -31681,40 +31694,37 @@
         </is>
       </c>
       <c r="E294" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I294" t="inlineStr"/>
-      <c r="J294" t="inlineStr"/>
-      <c r="K294" t="inlineStr"/>
-      <c r="N294" t="inlineStr"/>
       <c r="P294" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q294" t="n">
-        <v>427249</v>
+        <v>427504</v>
       </c>
       <c r="R294" t="n">
-        <v>6798389</v>
+        <v>6798429</v>
       </c>
       <c r="S294" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T294" t="inlineStr">
         <is>
@@ -31743,7 +31753,7 @@
       </c>
       <c r="Z294" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA294" t="inlineStr">
@@ -31753,12 +31763,7 @@
       </c>
       <c r="AB294" t="inlineStr">
         <is>
-          <t>12:36</t>
-        </is>
-      </c>
-      <c r="AC294" t="inlineStr">
-        <is>
-          <t>Brandstubbe</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD294" t="b">
@@ -31767,29 +31772,28 @@
       <c r="AE294" t="b">
         <v>0</v>
       </c>
-      <c r="AF294" t="inlineStr"/>
       <c r="AG294" t="b">
         <v>0</v>
       </c>
       <c r="AT294" t="inlineStr"/>
       <c r="AW294" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX294" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>133570842</v>
+        <v>133570353</v>
       </c>
       <c r="B295" t="n">
-        <v>79090</v>
+        <v>79333</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -31797,40 +31801,37 @@
         </is>
       </c>
       <c r="E295" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I295" t="inlineStr"/>
-      <c r="J295" t="inlineStr"/>
-      <c r="K295" t="inlineStr"/>
-      <c r="N295" t="inlineStr"/>
       <c r="P295" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q295" t="n">
-        <v>426905</v>
+        <v>427523</v>
       </c>
       <c r="R295" t="n">
-        <v>6798726</v>
+        <v>6798453</v>
       </c>
       <c r="S295" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T295" t="inlineStr">
         <is>
@@ -31859,7 +31860,7 @@
       </c>
       <c r="Z295" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA295" t="inlineStr">
@@ -31869,7 +31870,7 @@
       </c>
       <c r="AB295" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD295" t="b">
@@ -31878,19 +31879,18 @@
       <c r="AE295" t="b">
         <v>0</v>
       </c>
-      <c r="AF295" t="inlineStr"/>
       <c r="AG295" t="b">
         <v>0</v>
       </c>
       <c r="AT295" t="inlineStr"/>
       <c r="AW295" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX295" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY295" t="inlineStr"/>
@@ -32236,10 +32236,10 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>133570830</v>
+        <v>133570780</v>
       </c>
       <c r="B299" t="n">
-        <v>57955</v>
+        <v>79952</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -32247,39 +32247,34 @@
         </is>
       </c>
       <c r="E299" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I299" t="inlineStr"/>
-      <c r="M299" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P299" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q299" t="n">
-        <v>426912</v>
+        <v>427229</v>
       </c>
       <c r="R299" t="n">
-        <v>6798798</v>
+        <v>6798492</v>
       </c>
       <c r="S299" t="n">
         <v>10</v>
@@ -32311,7 +32306,7 @@
       </c>
       <c r="Z299" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA299" t="inlineStr">
@@ -32321,12 +32316,7 @@
       </c>
       <c r="AB299" t="inlineStr">
         <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="AC299" t="inlineStr">
-        <is>
-          <t>10.00</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD299" t="b">
@@ -32353,10 +32343,10 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>133570784</v>
+        <v>133570351</v>
       </c>
       <c r="B300" t="n">
-        <v>57955</v>
+        <v>79333</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -32364,42 +32354,37 @@
         </is>
       </c>
       <c r="E300" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I300" t="inlineStr"/>
-      <c r="M300" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P300" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q300" t="n">
-        <v>427227</v>
+        <v>427528</v>
       </c>
       <c r="R300" t="n">
-        <v>6798423</v>
+        <v>6798510</v>
       </c>
       <c r="S300" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T300" t="inlineStr">
         <is>
@@ -32428,7 +32413,7 @@
       </c>
       <c r="Z300" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA300" t="inlineStr">
@@ -32438,7 +32423,7 @@
       </c>
       <c r="AB300" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD300" t="b">
@@ -32453,22 +32438,22 @@
       <c r="AT300" t="inlineStr"/>
       <c r="AW300" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX300" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>133570868</v>
+        <v>133570350</v>
       </c>
       <c r="B301" t="n">
-        <v>57955</v>
+        <v>79333</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -32476,42 +32461,37 @@
         </is>
       </c>
       <c r="E301" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I301" t="inlineStr"/>
-      <c r="M301" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P301" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q301" t="n">
-        <v>426866</v>
+        <v>427523</v>
       </c>
       <c r="R301" t="n">
-        <v>6798608</v>
+        <v>6798536</v>
       </c>
       <c r="S301" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="T301" t="inlineStr">
         <is>
@@ -32540,7 +32520,7 @@
       </c>
       <c r="Z301" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA301" t="inlineStr">
@@ -32550,7 +32530,7 @@
       </c>
       <c r="AB301" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD301" t="b">
@@ -32565,12 +32545,12 @@
       <c r="AT301" t="inlineStr"/>
       <c r="AW301" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX301" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY301" t="inlineStr"/>
@@ -32684,10 +32664,10 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>133570780</v>
+        <v>133570868</v>
       </c>
       <c r="B303" t="n">
-        <v>79952</v>
+        <v>57955</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -32695,34 +32675,39 @@
         </is>
       </c>
       <c r="E303" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I303" t="inlineStr"/>
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P303" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q303" t="n">
-        <v>427229</v>
+        <v>426866</v>
       </c>
       <c r="R303" t="n">
-        <v>6798492</v>
+        <v>6798608</v>
       </c>
       <c r="S303" t="n">
         <v>10</v>
@@ -32754,7 +32739,7 @@
       </c>
       <c r="Z303" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA303" t="inlineStr">
@@ -32764,7 +32749,7 @@
       </c>
       <c r="AB303" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD303" t="b">
@@ -32791,10 +32776,10 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>133570351</v>
+        <v>133570830</v>
       </c>
       <c r="B304" t="n">
-        <v>79333</v>
+        <v>57955</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -32802,37 +32787,42 @@
         </is>
       </c>
       <c r="E304" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I304" t="inlineStr"/>
+      <c r="M304" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P304" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q304" t="n">
-        <v>427528</v>
+        <v>426912</v>
       </c>
       <c r="R304" t="n">
-        <v>6798510</v>
+        <v>6798798</v>
       </c>
       <c r="S304" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T304" t="inlineStr">
         <is>
@@ -32861,7 +32851,7 @@
       </c>
       <c r="Z304" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA304" t="inlineStr">
@@ -32871,7 +32861,12 @@
       </c>
       <c r="AB304" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC304" t="inlineStr">
+        <is>
+          <t>10.00</t>
         </is>
       </c>
       <c r="AD304" t="b">
@@ -32886,22 +32881,22 @@
       <c r="AT304" t="inlineStr"/>
       <c r="AW304" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX304" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>133570350</v>
+        <v>133570784</v>
       </c>
       <c r="B305" t="n">
-        <v>79333</v>
+        <v>57955</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -32909,37 +32904,42 @@
         </is>
       </c>
       <c r="E305" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I305" t="inlineStr"/>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P305" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q305" t="n">
-        <v>427523</v>
+        <v>427227</v>
       </c>
       <c r="R305" t="n">
-        <v>6798536</v>
+        <v>6798423</v>
       </c>
       <c r="S305" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="T305" t="inlineStr">
         <is>
@@ -32968,7 +32968,7 @@
       </c>
       <c r="Z305" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA305" t="inlineStr">
@@ -32978,7 +32978,7 @@
       </c>
       <c r="AB305" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD305" t="b">
@@ -32993,12 +32993,12 @@
       <c r="AT305" t="inlineStr"/>
       <c r="AW305" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX305" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY305" t="inlineStr"/>
@@ -33112,10 +33112,10 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>133570741</v>
+        <v>133570761</v>
       </c>
       <c r="B307" t="n">
-        <v>79333</v>
+        <v>79952</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -33123,21 +33123,21 @@
         </is>
       </c>
       <c r="E307" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I307" t="inlineStr"/>
@@ -33147,10 +33147,10 @@
         </is>
       </c>
       <c r="Q307" t="n">
-        <v>427501</v>
+        <v>427305</v>
       </c>
       <c r="R307" t="n">
-        <v>6798480</v>
+        <v>6798750</v>
       </c>
       <c r="S307" t="n">
         <v>10</v>
@@ -33182,7 +33182,7 @@
       </c>
       <c r="Z307" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA307" t="inlineStr">
@@ -33192,7 +33192,7 @@
       </c>
       <c r="AB307" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD307" t="b">
@@ -33219,7 +33219,7 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>133570348</v>
+        <v>133570741</v>
       </c>
       <c r="B308" t="n">
         <v>79333</v>
@@ -33254,13 +33254,13 @@
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>427509</v>
+        <v>427501</v>
       </c>
       <c r="R308" t="n">
-        <v>6798594</v>
+        <v>6798480</v>
       </c>
       <c r="S308" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T308" t="inlineStr">
         <is>
@@ -33289,7 +33289,7 @@
       </c>
       <c r="Z308" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA308" t="inlineStr">
@@ -33299,7 +33299,7 @@
       </c>
       <c r="AB308" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD308" t="b">
@@ -33314,22 +33314,22 @@
       <c r="AT308" t="inlineStr"/>
       <c r="AW308" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX308" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>133570761</v>
+        <v>133570348</v>
       </c>
       <c r="B309" t="n">
-        <v>79952</v>
+        <v>79333</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -33337,21 +33337,21 @@
         </is>
       </c>
       <c r="E309" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I309" t="inlineStr"/>
@@ -33361,13 +33361,13 @@
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>427305</v>
+        <v>427509</v>
       </c>
       <c r="R309" t="n">
-        <v>6798750</v>
+        <v>6798594</v>
       </c>
       <c r="S309" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T309" t="inlineStr">
         <is>
@@ -33396,7 +33396,7 @@
       </c>
       <c r="Z309" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA309" t="inlineStr">
@@ -33406,7 +33406,7 @@
       </c>
       <c r="AB309" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD309" t="b">
@@ -33421,12 +33421,12 @@
       <c r="AT309" t="inlineStr"/>
       <c r="AW309" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX309" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY309" t="inlineStr"/>
@@ -33657,32 +33657,32 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>133570754</v>
+        <v>133570744</v>
       </c>
       <c r="B312" t="n">
-        <v>98001</v>
+        <v>79090</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E312" t="n">
-        <v>221941</v>
+        <v>6446</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I312" t="inlineStr"/>
@@ -33692,10 +33692,10 @@
         </is>
       </c>
       <c r="Q312" t="n">
-        <v>427512</v>
+        <v>427459</v>
       </c>
       <c r="R312" t="n">
-        <v>6798623</v>
+        <v>6798536</v>
       </c>
       <c r="S312" t="n">
         <v>10</v>
@@ -33727,7 +33727,7 @@
       </c>
       <c r="Z312" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA312" t="inlineStr">
@@ -33737,7 +33737,7 @@
       </c>
       <c r="AB312" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD312" t="b">
@@ -33764,10 +33764,10 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>133570744</v>
+        <v>133570855</v>
       </c>
       <c r="B313" t="n">
-        <v>79090</v>
+        <v>79952</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -33775,21 +33775,21 @@
         </is>
       </c>
       <c r="E313" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I313" t="inlineStr"/>
@@ -33799,10 +33799,10 @@
         </is>
       </c>
       <c r="Q313" t="n">
-        <v>427459</v>
+        <v>426909</v>
       </c>
       <c r="R313" t="n">
-        <v>6798536</v>
+        <v>6798629</v>
       </c>
       <c r="S313" t="n">
         <v>10</v>
@@ -33834,7 +33834,7 @@
       </c>
       <c r="Z313" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA313" t="inlineStr">
@@ -33844,7 +33844,7 @@
       </c>
       <c r="AB313" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD313" t="b">
@@ -33871,10 +33871,10 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>133570337</v>
+        <v>133570843</v>
       </c>
       <c r="B314" t="n">
-        <v>79333</v>
+        <v>58119</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -33882,37 +33882,45 @@
         </is>
       </c>
       <c r="E314" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I314" t="inlineStr"/>
+      <c r="K314" t="inlineStr"/>
+      <c r="L314" t="inlineStr"/>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N314" t="inlineStr"/>
       <c r="P314" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q314" t="n">
-        <v>427280</v>
+        <v>426918</v>
       </c>
       <c r="R314" t="n">
-        <v>6798728</v>
+        <v>6798710</v>
       </c>
       <c r="S314" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T314" t="inlineStr">
         <is>
@@ -33941,7 +33949,7 @@
       </c>
       <c r="Z314" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA314" t="inlineStr">
@@ -33951,7 +33959,7 @@
       </c>
       <c r="AB314" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD314" t="b">
@@ -33966,22 +33974,22 @@
       <c r="AT314" t="inlineStr"/>
       <c r="AW314" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX314" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>133570855</v>
+        <v>133570337</v>
       </c>
       <c r="B315" t="n">
-        <v>79952</v>
+        <v>79333</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -33989,21 +33997,21 @@
         </is>
       </c>
       <c r="E315" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I315" t="inlineStr"/>
@@ -34013,13 +34021,13 @@
         </is>
       </c>
       <c r="Q315" t="n">
-        <v>426909</v>
+        <v>427280</v>
       </c>
       <c r="R315" t="n">
-        <v>6798629</v>
+        <v>6798728</v>
       </c>
       <c r="S315" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T315" t="inlineStr">
         <is>
@@ -34048,7 +34056,7 @@
       </c>
       <c r="Z315" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA315" t="inlineStr">
@@ -34058,7 +34066,7 @@
       </c>
       <c r="AB315" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD315" t="b">
@@ -34073,65 +34081,57 @@
       <c r="AT315" t="inlineStr"/>
       <c r="AW315" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX315" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>133570843</v>
+        <v>133570754</v>
       </c>
       <c r="B316" t="n">
-        <v>58119</v>
+        <v>98001</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E316" t="n">
-        <v>103021</v>
+        <v>221941</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I316" t="inlineStr"/>
-      <c r="K316" t="inlineStr"/>
-      <c r="L316" t="inlineStr"/>
-      <c r="M316" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N316" t="inlineStr"/>
       <c r="P316" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q316" t="n">
-        <v>426918</v>
+        <v>427512</v>
       </c>
       <c r="R316" t="n">
-        <v>6798710</v>
+        <v>6798623</v>
       </c>
       <c r="S316" t="n">
         <v>10</v>
@@ -34163,7 +34163,7 @@
       </c>
       <c r="Z316" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA316" t="inlineStr">
@@ -34173,7 +34173,7 @@
       </c>
       <c r="AB316" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD316" t="b">
@@ -34197,6 +34197,686 @@
         </is>
       </c>
       <c r="AY316" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" t="n">
+        <v>133639544</v>
+      </c>
+      <c r="B317" t="n">
+        <v>57145</v>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E317" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr"/>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P317" t="inlineStr">
+        <is>
+          <t>Mjölkbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q317" t="n">
+        <v>427615</v>
+      </c>
+      <c r="R317" t="n">
+        <v>6798424</v>
+      </c>
+      <c r="S317" t="n">
+        <v>10</v>
+      </c>
+      <c r="T317" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U317" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V317" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W317" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y317" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="Z317" t="inlineStr">
+        <is>
+          <t>18:16</t>
+        </is>
+      </c>
+      <c r="AA317" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AB317" t="inlineStr">
+        <is>
+          <t>18:16</t>
+        </is>
+      </c>
+      <c r="AD317" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE317" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG317" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT317" t="inlineStr"/>
+      <c r="AW317" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX317" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY317" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" t="n">
+        <v>133639543</v>
+      </c>
+      <c r="B318" t="n">
+        <v>57145</v>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E318" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr"/>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P318" t="inlineStr">
+        <is>
+          <t>Mjölkbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q318" t="n">
+        <v>427621</v>
+      </c>
+      <c r="R318" t="n">
+        <v>6798409</v>
+      </c>
+      <c r="S318" t="n">
+        <v>10</v>
+      </c>
+      <c r="T318" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U318" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V318" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W318" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y318" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="Z318" t="inlineStr">
+        <is>
+          <t>18:18</t>
+        </is>
+      </c>
+      <c r="AA318" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AB318" t="inlineStr">
+        <is>
+          <t>18:18</t>
+        </is>
+      </c>
+      <c r="AD318" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE318" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG318" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT318" t="inlineStr"/>
+      <c r="AW318" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX318" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY318" t="inlineStr"/>
+    </row>
+    <row r="319">
+      <c r="A319" t="n">
+        <v>133639541</v>
+      </c>
+      <c r="B319" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E319" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr"/>
+      <c r="K319" t="inlineStr"/>
+      <c r="L319" t="inlineStr"/>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N319" t="inlineStr"/>
+      <c r="P319" t="inlineStr">
+        <is>
+          <t>Mjölkbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q319" t="n">
+        <v>427626</v>
+      </c>
+      <c r="R319" t="n">
+        <v>6798407</v>
+      </c>
+      <c r="S319" t="n">
+        <v>10</v>
+      </c>
+      <c r="T319" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U319" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V319" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W319" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y319" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="Z319" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
+      <c r="AA319" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AB319" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
+      <c r="AD319" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE319" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG319" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT319" t="inlineStr"/>
+      <c r="AW319" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX319" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY319" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" t="n">
+        <v>133639540</v>
+      </c>
+      <c r="B320" t="n">
+        <v>57145</v>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E320" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr"/>
+      <c r="M320" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P320" t="inlineStr">
+        <is>
+          <t>Mjölkbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q320" t="n">
+        <v>427610</v>
+      </c>
+      <c r="R320" t="n">
+        <v>6798403</v>
+      </c>
+      <c r="S320" t="n">
+        <v>10</v>
+      </c>
+      <c r="T320" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U320" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V320" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W320" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y320" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="Z320" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AA320" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AB320" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AD320" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE320" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG320" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT320" t="inlineStr"/>
+      <c r="AW320" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX320" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY320" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" t="n">
+        <v>133639539</v>
+      </c>
+      <c r="B321" t="n">
+        <v>57145</v>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E321" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr"/>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P321" t="inlineStr">
+        <is>
+          <t>Mjölkbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q321" t="n">
+        <v>427587</v>
+      </c>
+      <c r="R321" t="n">
+        <v>6798417</v>
+      </c>
+      <c r="S321" t="n">
+        <v>10</v>
+      </c>
+      <c r="T321" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U321" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V321" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W321" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y321" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="Z321" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="AA321" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AB321" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="AD321" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE321" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG321" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT321" t="inlineStr"/>
+      <c r="AW321" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX321" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY321" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="A322" t="n">
+        <v>133639538</v>
+      </c>
+      <c r="B322" t="n">
+        <v>99130</v>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E322" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr"/>
+      <c r="J322" t="inlineStr"/>
+      <c r="K322" t="inlineStr"/>
+      <c r="L322" t="inlineStr"/>
+      <c r="N322" t="inlineStr"/>
+      <c r="P322" t="inlineStr">
+        <is>
+          <t>Mjölkbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q322" t="n">
+        <v>427615</v>
+      </c>
+      <c r="R322" t="n">
+        <v>6798415</v>
+      </c>
+      <c r="S322" t="n">
+        <v>10</v>
+      </c>
+      <c r="T322" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U322" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V322" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W322" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y322" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="Z322" t="inlineStr">
+        <is>
+          <t>18:54</t>
+        </is>
+      </c>
+      <c r="AA322" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AB322" t="inlineStr">
+        <is>
+          <t>18:54</t>
+        </is>
+      </c>
+      <c r="AC322" t="inlineStr">
+        <is>
+          <t>I avverkningsanmälningen rikligt med knärötter inom en radie av 4 meter. Snitslar för naturvårdshänsyn verkar saknas runt dessa. Dessutom endast 30 meter ner till hyggeskanten.</t>
+        </is>
+      </c>
+      <c r="AD322" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE322" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF322" t="inlineStr"/>
+      <c r="AG322" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT322" t="inlineStr"/>
+      <c r="AW322" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX322" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY322" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4832-2026 artfynd.xlsx
+++ b/artfynd/A 4832-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY339"/>
+  <dimension ref="A1:AZ339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126335625</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126365118</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126338600</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126022301</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126022320</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126022321</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1381,6 +1416,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126022322</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1478,6 +1518,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126339529</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1590,6 +1635,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570313</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1702,6 +1752,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570342</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1809,6 +1864,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570344</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1920,6 +1980,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570747</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2031,6 +2096,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570753</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2138,6 +2208,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570759</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2249,6 +2324,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570782</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2364,6 +2444,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570808</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2479,6 +2564,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570818</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2576,6 +2666,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126022313</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2673,6 +2768,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126022317</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2770,6 +2870,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126022318</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2867,6 +2972,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126333986</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2974,6 +3084,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126334331</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3086,6 +3201,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126334762</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3193,6 +3313,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126334764</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3300,6 +3425,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126334857</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3397,6 +3527,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126335181</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3504,6 +3639,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126335214</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3601,6 +3741,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126335672</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3708,6 +3853,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126337016</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3815,6 +3965,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126339880</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3922,6 +4077,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126340016</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4029,6 +4189,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126340385</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4136,6 +4301,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126340434</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4233,6 +4403,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126377507</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4330,6 +4505,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126377508</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4437,6 +4617,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570337</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4544,6 +4729,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570341</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4655,6 +4845,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570345</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4762,6 +4957,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570346</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4869,6 +5069,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570348</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4976,6 +5181,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570350</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5083,6 +5293,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570351</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5190,6 +5405,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570353</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5297,6 +5517,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570357</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5404,6 +5629,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570361</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5511,6 +5741,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570362</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5618,6 +5853,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570729</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5725,6 +5965,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570733</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5832,6 +6077,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570738</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5939,6 +6189,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570739</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6046,6 +6301,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570740</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6153,6 +6413,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570741</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6260,6 +6525,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570751</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6367,6 +6637,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570755</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6474,6 +6749,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570766</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6581,6 +6861,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570768</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6688,6 +6973,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570769</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6795,6 +7085,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126364364</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6892,6 +7187,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126022285</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6989,6 +7289,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126022315</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7086,6 +7391,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126022316</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7193,6 +7503,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126335881</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7300,6 +7615,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126336092</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7407,6 +7727,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126337074</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7504,6 +7829,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126337688</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7611,6 +7941,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126337982</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7718,6 +8053,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126338143</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7825,6 +8165,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126338368</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7932,6 +8277,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126338668</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8039,6 +8389,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126338801</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8136,6 +8491,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126338818</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8243,6 +8603,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126339416</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8350,6 +8715,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126339616</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8457,6 +8827,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126339757</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8554,6 +8929,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126339770</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8661,6 +9041,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126340359</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8768,6 +9153,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126340584</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8875,6 +9265,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126340669</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8972,6 +9367,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126377478</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9069,6 +9469,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126377479</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9181,6 +9586,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570319</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9288,6 +9698,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570321</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9404,6 +9819,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570325</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9516,6 +9936,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570328</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9623,6 +10048,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570340</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9734,6 +10164,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570349</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9841,6 +10276,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570744</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9948,6 +10388,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570767</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10055,6 +10500,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570781</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10162,6 +10612,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570788</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10269,6 +10724,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570802</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10376,6 +10836,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570806</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10483,6 +10948,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570815</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10590,6 +11060,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570828</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10701,6 +11176,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570842</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10808,6 +11288,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570846</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10915,6 +11400,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570849</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11026,6 +11516,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570856</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11133,6 +11628,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570857</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11230,6 +11730,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126022284</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11327,6 +11832,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126022288</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11424,6 +11934,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126022289</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11521,6 +12036,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126022290</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11618,6 +12138,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126022291</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11715,6 +12240,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126022292</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11812,6 +12342,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126022293</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11909,6 +12444,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126022294</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12006,6 +12546,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126022303</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12103,6 +12648,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126022306</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12210,6 +12760,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126334052</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12317,6 +12872,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126334237</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12424,6 +12984,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126334320</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12531,6 +13096,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126334548</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12638,6 +13208,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126334554</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12745,6 +13320,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126334576</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12852,6 +13432,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126334889</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12949,6 +13534,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126335594</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13060,6 +13650,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126335754</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13167,6 +13762,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126335762</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13274,6 +13874,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126335972</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13371,6 +13976,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126335998</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13478,6 +14088,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126336082</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13575,6 +14190,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126336252</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13682,6 +14302,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126337209</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13779,6 +14404,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126337227</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13886,6 +14516,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126337254</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13993,6 +14628,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126337559</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14090,6 +14730,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126337677</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14197,6 +14842,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126337748</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14294,6 +14944,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126337810</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14401,6 +15056,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126337975</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14508,6 +15168,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126338320</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14615,6 +15280,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126338455</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14722,6 +15392,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126338799</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14829,6 +15504,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126339121</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14936,6 +15616,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126339304</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -15043,6 +15728,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126339405</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15150,6 +15840,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126339444</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -15257,6 +15952,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126339773</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15364,6 +16064,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126339860</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15471,6 +16176,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126339899</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15578,6 +16288,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126340365</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15678,6 +16393,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126377421</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -15778,6 +16498,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126377422</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15878,6 +16603,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126377423</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15978,6 +16708,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126377424</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -16078,6 +16813,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126377425</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -16178,6 +16918,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126377426</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -16279,6 +17024,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126377427</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -16391,6 +17141,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570315</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -16503,6 +17258,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570318</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -16610,6 +17370,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570322</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -16717,6 +17482,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570761</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -16824,6 +17594,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570780</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -16931,6 +17706,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570789</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -17042,6 +17822,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570790</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -17153,6 +17938,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570791</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -17260,6 +18050,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570792</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -17367,6 +18162,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570793</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -17474,6 +18274,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570795</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -17581,6 +18386,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570796</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -17688,6 +18498,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570797</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -17795,6 +18610,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570798</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -17902,6 +18722,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570800</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -18009,6 +18834,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570803</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -18116,6 +18946,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570804</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -18223,6 +19058,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570813</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -18330,6 +19170,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570816</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -18437,6 +19282,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570819</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -18544,6 +19394,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570820</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -18655,6 +19510,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570821</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -18762,6 +19622,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570825</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -18869,6 +19734,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570827</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -18976,6 +19846,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570831</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -19083,6 +19958,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570845</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -19194,6 +20074,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570850</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -19301,6 +20186,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570851</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -19408,6 +20298,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570852</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -19515,6 +20410,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570855</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -19622,6 +20522,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570860</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -19729,6 +20634,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570862</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -19836,6 +20746,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570863</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -19943,6 +20858,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570867</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -20050,6 +20970,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126364681</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -20157,6 +21082,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570811</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -20269,6 +21199,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126337970</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -20371,6 +21306,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126339364</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -20483,6 +21423,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570311</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -20595,6 +21540,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570326</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -20707,6 +21657,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570336</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -20819,6 +21774,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570339</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -20931,6 +21891,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570363</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -21043,6 +22008,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570720</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -21155,6 +22125,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570727</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -21267,6 +22242,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570743</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -21379,6 +22359,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570749</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -21491,6 +22476,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570752</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -21603,6 +22593,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570757</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -21715,6 +22710,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570760</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -21830,6 +22830,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570764</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -21942,6 +22947,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570765</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -22054,6 +23064,11 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570770</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -22166,6 +23181,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570771</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -22278,6 +23298,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570784</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -22390,6 +23415,11 @@
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570785</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -22502,6 +23532,11 @@
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570786</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -22614,6 +23649,11 @@
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570807</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -22726,6 +23766,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570810</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -22838,6 +23883,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570814</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -22950,6 +24000,11 @@
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570817</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -23067,6 +24122,11 @@
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570830</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -23179,6 +24239,11 @@
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570868</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -23291,6 +24356,11 @@
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570869</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -23406,6 +24476,11 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133639541</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -23508,6 +24583,11 @@
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126335481</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -23623,6 +24703,11 @@
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570721</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -23743,6 +24828,11 @@
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570732</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -23863,6 +24953,11 @@
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570756</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -23965,6 +25060,11 @@
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126377429</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -24077,6 +25177,11 @@
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570324</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -24189,6 +25294,11 @@
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570329</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -24301,6 +25411,11 @@
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570330</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -24413,6 +25528,11 @@
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570331</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -24525,6 +25645,11 @@
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570333</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -24637,6 +25762,11 @@
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570334</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -24749,6 +25879,11 @@
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570335</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -24861,6 +25996,11 @@
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570358</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -24973,6 +26113,11 @@
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570725</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -25085,6 +26230,11 @@
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570742</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -25197,6 +26347,11 @@
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570746</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -25309,6 +26464,11 @@
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570748</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -25421,6 +26581,11 @@
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570758</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -25533,6 +26698,11 @@
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570772</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -25645,6 +26815,11 @@
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570774</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -25757,6 +26932,11 @@
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570776</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -25872,6 +27052,11 @@
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570778</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -25987,6 +27172,11 @@
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570779</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -26102,6 +27292,11 @@
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570783</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -26214,6 +27409,11 @@
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570787</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -26329,6 +27529,11 @@
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570871</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -26441,6 +27646,11 @@
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133639539</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -26553,6 +27763,11 @@
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133639540</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -26665,6 +27880,11 @@
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133639543</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -26777,6 +27997,11 @@
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133639544</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -26892,6 +28117,11 @@
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570834</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -26994,6 +28224,11 @@
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126335337</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -27091,6 +28326,11 @@
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126022298</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -27197,6 +28437,11 @@
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126022299</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -27299,6 +28544,11 @@
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126335852</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -27414,6 +28664,11 @@
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570832</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -27529,6 +28784,11 @@
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570843</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -27631,6 +28891,11 @@
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126334241</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -27743,6 +29008,11 @@
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126335831</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -27860,6 +29130,11 @@
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570858</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -27972,6 +29247,11 @@
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570360</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -28084,6 +29364,11 @@
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570762</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -28201,6 +29486,11 @@
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126334915</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -28312,6 +29602,11 @@
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126335072</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -28409,6 +29704,11 @@
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
+      <c r="AZ260" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126335099</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -28516,6 +29816,11 @@
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126335973</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -28623,6 +29928,11 @@
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
+      <c r="AZ262" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126336022</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -28730,6 +30040,11 @@
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
+      <c r="AZ263" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126336097</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -28847,6 +30162,11 @@
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
+      <c r="AZ264" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126340047</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -28954,6 +30274,11 @@
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
+      <c r="AZ265" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126340128</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -29061,6 +30386,11 @@
         </is>
       </c>
       <c r="AY266" t="inlineStr"/>
+      <c r="AZ266" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570730</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -29168,6 +30498,11 @@
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
+      <c r="AZ267" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570836</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -29285,6 +30620,11 @@
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
+      <c r="AZ268" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133639538</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -29406,6 +30746,11 @@
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
+      <c r="AZ269" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133641919</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -29513,6 +30858,11 @@
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
+      <c r="AZ270" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570731</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -29620,6 +30970,11 @@
         </is>
       </c>
       <c r="AY271" t="inlineStr"/>
+      <c r="AZ271" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570838</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -29727,6 +31082,11 @@
         </is>
       </c>
       <c r="AY272" t="inlineStr"/>
+      <c r="AZ272" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570840</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -29834,6 +31194,11 @@
         </is>
       </c>
       <c r="AY273" t="inlineStr"/>
+      <c r="AZ273" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570754</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -29946,6 +31311,11 @@
         </is>
       </c>
       <c r="AY274" t="inlineStr"/>
+      <c r="AZ274" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570835</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -30048,6 +31418,11 @@
         </is>
       </c>
       <c r="AY275" t="inlineStr"/>
+      <c r="AZ275" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126377430</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -30150,6 +31525,11 @@
         </is>
       </c>
       <c r="AY276" t="inlineStr"/>
+      <c r="AZ276" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126377431</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -30257,6 +31637,11 @@
         </is>
       </c>
       <c r="AY277" t="inlineStr"/>
+      <c r="AZ277" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570736</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -30369,6 +31754,11 @@
         </is>
       </c>
       <c r="AY278" t="inlineStr"/>
+      <c r="AZ278" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570763</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -30466,6 +31856,11 @@
         </is>
       </c>
       <c r="AY279" t="inlineStr"/>
+      <c r="AZ279" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126022304</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -30563,6 +31958,11 @@
         </is>
       </c>
       <c r="AY280" t="inlineStr"/>
+      <c r="AZ280" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126022309</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -30660,6 +32060,11 @@
         </is>
       </c>
       <c r="AY281" t="inlineStr"/>
+      <c r="AZ281" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126022310</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -30757,6 +32162,11 @@
         </is>
       </c>
       <c r="AY282" t="inlineStr"/>
+      <c r="AZ282" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126022311</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -30854,6 +32264,11 @@
         </is>
       </c>
       <c r="AY283" t="inlineStr"/>
+      <c r="AZ283" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126022312</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -30961,6 +32376,11 @@
         </is>
       </c>
       <c r="AY284" t="inlineStr"/>
+      <c r="AZ284" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126334541</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -31068,6 +32488,11 @@
         </is>
       </c>
       <c r="AY285" t="inlineStr"/>
+      <c r="AZ285" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126334876</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -31184,6 +32609,11 @@
         </is>
       </c>
       <c r="AY286" t="inlineStr"/>
+      <c r="AZ286" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126335508</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -31291,6 +32721,11 @@
         </is>
       </c>
       <c r="AY287" t="inlineStr"/>
+      <c r="AZ287" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126335567</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -31388,6 +32823,11 @@
         </is>
       </c>
       <c r="AY288" t="inlineStr"/>
+      <c r="AZ288" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126335613</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -31495,6 +32935,11 @@
         </is>
       </c>
       <c r="AY289" t="inlineStr"/>
+      <c r="AZ289" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126335795</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -31602,6 +33047,11 @@
         </is>
       </c>
       <c r="AY290" t="inlineStr"/>
+      <c r="AZ290" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126335896</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -31709,6 +33159,11 @@
         </is>
       </c>
       <c r="AY291" t="inlineStr"/>
+      <c r="AZ291" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126336106</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -31810,6 +33265,11 @@
         </is>
       </c>
       <c r="AY292" t="inlineStr"/>
+      <c r="AZ292" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126336234</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -31907,6 +33367,11 @@
         </is>
       </c>
       <c r="AY293" t="inlineStr"/>
+      <c r="AZ293" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126336279</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -32014,6 +33479,11 @@
         </is>
       </c>
       <c r="AY294" t="inlineStr"/>
+      <c r="AZ294" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126337286</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -32111,6 +33581,11 @@
         </is>
       </c>
       <c r="AY295" t="inlineStr"/>
+      <c r="AZ295" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126337563</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -32218,6 +33693,11 @@
         </is>
       </c>
       <c r="AY296" t="inlineStr"/>
+      <c r="AZ296" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126337979</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -32325,6 +33805,11 @@
         </is>
       </c>
       <c r="AY297" t="inlineStr"/>
+      <c r="AZ297" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126338051</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -32432,6 +33917,11 @@
         </is>
       </c>
       <c r="AY298" t="inlineStr"/>
+      <c r="AZ298" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126338355</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -32539,6 +34029,11 @@
         </is>
       </c>
       <c r="AY299" t="inlineStr"/>
+      <c r="AZ299" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126338943</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -32646,6 +34141,11 @@
         </is>
       </c>
       <c r="AY300" t="inlineStr"/>
+      <c r="AZ300" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126339028</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -32753,6 +34253,11 @@
         </is>
       </c>
       <c r="AY301" t="inlineStr"/>
+      <c r="AZ301" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126339359</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -32860,6 +34365,11 @@
         </is>
       </c>
       <c r="AY302" t="inlineStr"/>
+      <c r="AZ302" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126339407</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -32967,6 +34477,11 @@
         </is>
       </c>
       <c r="AY303" t="inlineStr"/>
+      <c r="AZ303" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126339573</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -33074,6 +34589,11 @@
         </is>
       </c>
       <c r="AY304" t="inlineStr"/>
+      <c r="AZ304" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126339588</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -33181,6 +34701,11 @@
         </is>
       </c>
       <c r="AY305" t="inlineStr"/>
+      <c r="AZ305" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126339857</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -33288,6 +34813,11 @@
         </is>
       </c>
       <c r="AY306" t="inlineStr"/>
+      <c r="AZ306" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126339948</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -33385,6 +34915,11 @@
         </is>
       </c>
       <c r="AY307" t="inlineStr"/>
+      <c r="AZ307" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126377455</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -33482,6 +35017,11 @@
         </is>
       </c>
       <c r="AY308" t="inlineStr"/>
+      <c r="AZ308" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126377456</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -33579,6 +35119,11 @@
         </is>
       </c>
       <c r="AY309" t="inlineStr"/>
+      <c r="AZ309" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126377457</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -33676,6 +35221,11 @@
         </is>
       </c>
       <c r="AY310" t="inlineStr"/>
+      <c r="AZ310" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126377458</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -33773,6 +35323,11 @@
         </is>
       </c>
       <c r="AY311" t="inlineStr"/>
+      <c r="AZ311" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126377459</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -33885,6 +35440,11 @@
         </is>
       </c>
       <c r="AY312" t="inlineStr"/>
+      <c r="AZ312" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570317</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -33996,6 +35556,11 @@
         </is>
       </c>
       <c r="AY313" t="inlineStr"/>
+      <c r="AZ313" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570320</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -34107,6 +35672,11 @@
         </is>
       </c>
       <c r="AY314" t="inlineStr"/>
+      <c r="AZ314" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570794</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -34214,6 +35784,11 @@
         </is>
       </c>
       <c r="AY315" t="inlineStr"/>
+      <c r="AZ315" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570805</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -34321,6 +35896,11 @@
         </is>
       </c>
       <c r="AY316" t="inlineStr"/>
+      <c r="AZ316" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570824</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -34428,6 +36008,11 @@
         </is>
       </c>
       <c r="AY317" t="inlineStr"/>
+      <c r="AZ317" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570829</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -34535,6 +36120,11 @@
         </is>
       </c>
       <c r="AY318" t="inlineStr"/>
+      <c r="AZ318" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570841</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -34646,6 +36236,11 @@
         </is>
       </c>
       <c r="AY319" t="inlineStr"/>
+      <c r="AZ319" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570847</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -34753,6 +36348,11 @@
         </is>
       </c>
       <c r="AY320" t="inlineStr"/>
+      <c r="AZ320" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570861</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -34860,6 +36460,11 @@
         </is>
       </c>
       <c r="AY321" t="inlineStr"/>
+      <c r="AZ321" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570865</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -34957,6 +36562,11 @@
         </is>
       </c>
       <c r="AY322" t="inlineStr"/>
+      <c r="AZ322" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126022296</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -35054,6 +36664,11 @@
         </is>
       </c>
       <c r="AY323" t="inlineStr"/>
+      <c r="AZ323" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126022297</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -35151,6 +36766,11 @@
         </is>
       </c>
       <c r="AY324" t="inlineStr"/>
+      <c r="AZ324" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126335603</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -35248,6 +36868,11 @@
         </is>
       </c>
       <c r="AY325" t="inlineStr"/>
+      <c r="AZ325" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126337222</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -35355,6 +36980,11 @@
         </is>
       </c>
       <c r="AY326" t="inlineStr"/>
+      <c r="AZ326" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126337274</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -35452,6 +37082,11 @@
         </is>
       </c>
       <c r="AY327" t="inlineStr"/>
+      <c r="AZ327" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126337681</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -35549,6 +37184,11 @@
         </is>
       </c>
       <c r="AY328" t="inlineStr"/>
+      <c r="AZ328" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126337872</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -35656,6 +37296,11 @@
         </is>
       </c>
       <c r="AY329" t="inlineStr"/>
+      <c r="AZ329" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126338324</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -35763,6 +37408,11 @@
         </is>
       </c>
       <c r="AY330" t="inlineStr"/>
+      <c r="AZ330" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126338823</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -35870,6 +37520,11 @@
         </is>
       </c>
       <c r="AY331" t="inlineStr"/>
+      <c r="AZ331" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126339015</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -35977,6 +37632,11 @@
         </is>
       </c>
       <c r="AY332" t="inlineStr"/>
+      <c r="AZ332" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126339643</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -36084,6 +37744,11 @@
         </is>
       </c>
       <c r="AY333" t="inlineStr"/>
+      <c r="AZ333" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126339943</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -36191,6 +37856,11 @@
         </is>
       </c>
       <c r="AY334" t="inlineStr"/>
+      <c r="AZ334" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126340383</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -36303,6 +37973,11 @@
         </is>
       </c>
       <c r="AY335" t="inlineStr"/>
+      <c r="AZ335" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570314</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -36410,6 +38085,11 @@
         </is>
       </c>
       <c r="AY336" t="inlineStr"/>
+      <c r="AZ336" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570801</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -36517,6 +38197,11 @@
         </is>
       </c>
       <c r="AY337" t="inlineStr"/>
+      <c r="AZ337" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570812</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -36614,6 +38299,11 @@
         </is>
       </c>
       <c r="AY338" t="inlineStr"/>
+      <c r="AZ338" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126334607</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -36725,8 +38415,353 @@
         </is>
       </c>
       <c r="AY339" t="inlineStr"/>
+      <c r="AZ339" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133570338</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ269" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ270" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ271" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ272" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ273" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ274" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ275" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ276" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ277" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ278" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ279" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ280" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ281" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ282" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ283" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ284" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ285" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ286" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ287" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ288" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ289" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ290" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ291" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ292" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ293" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ294" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ295" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ296" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ297" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ298" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ299" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ300" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ301" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ302" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ303" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ304" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ305" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ306" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ307" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ308" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ309" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ310" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ311" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ312" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ313" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ314" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ315" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ316" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ317" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ318" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ319" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ320" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ321" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ322" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ323" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ324" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ325" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ326" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ327" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ328" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ329" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ330" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ331" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ332" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ333" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ334" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ335" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ336" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ337" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ338" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ339" r:id="rId338"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>